--- a/Notes/notes-COLOR_CONVERSION.xlsx
+++ b/Notes/notes-COLOR_CONVERSION.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\scrawford\silvermirror-local\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B8AFF2-65D2-4610-BC5D-FB28A3D646D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B5993B-3238-4A80-BE73-B7EEBE5AAE25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="-1035" windowWidth="14610" windowHeight="15585" xr2:uid="{EF373D87-73EE-428D-B1DE-10AFA67A5623}"/>
+    <workbookView xWindow="41280" yWindow="315" windowWidth="16050" windowHeight="12285" activeTab="1" xr2:uid="{EF373D87-73EE-428D-B1DE-10AFA67A5623}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="33">
   <si>
     <t>; pichu</t>
   </si>
@@ -82,6 +83,60 @@
   <si>
     <t>convert to 31</t>
   </si>
+  <si>
+    <t>31 to 255</t>
+  </si>
+  <si>
+    <t>255 to 31</t>
+  </si>
+  <si>
+    <t>; red</t>
+  </si>
+  <si>
+    <t>; blue</t>
+  </si>
+  <si>
+    <t>; green</t>
+  </si>
+  <si>
+    <t>; brown</t>
+  </si>
+  <si>
+    <t>; purple</t>
+  </si>
+  <si>
+    <t>; silver</t>
+  </si>
+  <si>
+    <t>; tree</t>
+  </si>
+  <si>
+    <t>; rock</t>
+  </si>
+  <si>
+    <t>; pink</t>
+  </si>
+  <si>
+    <t>; yellow</t>
+  </si>
+  <si>
+    <t>; grey</t>
+  </si>
+  <si>
+    <t>; black</t>
+  </si>
+  <si>
+    <t>; day</t>
+  </si>
+  <si>
+    <t>; eve</t>
+  </si>
+  <si>
+    <t>; morn \ eve</t>
+  </si>
+  <si>
+    <t>; nite \ dark</t>
+  </si>
 </sst>
 </file>
 
@@ -96,7 +151,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -109,8 +164,68 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC9900"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF669900"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC99FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -118,11 +233,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -131,13 +261,37 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFFF99"/>
+      <color rgb="FFCC99FF"/>
+      <color rgb="FFFFCCFF"/>
+      <color rgb="FFCC9900"/>
+      <color rgb="FF669900"/>
+      <color rgb="FFFFCC99"/>
+      <color rgb="FF996633"/>
+      <color rgb="FF9966FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -466,14 +620,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74B0A363-AE59-4EC5-8883-E61C63092E84}">
-  <dimension ref="A1:AH48"/>
+  <dimension ref="A1:AK42"/>
   <sheetFormatPr defaultColWidth="4.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="17" width="3.7109375" customWidth="1"/>
     <col min="19" max="19" width="7.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -495,8 +649,9 @@
       <c r="S1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AK1" s="12"/>
+    </row>
+    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>4</v>
@@ -543,8 +698,9 @@
       <c r="S2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AK2" s="12"/>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
         <v>4</v>
@@ -588,8 +744,9 @@
       <c r="Q3" s="1">
         <v>31</v>
       </c>
-    </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AK3" s="12"/>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
         <v>4</v>
@@ -636,8 +793,9 @@
       <c r="S4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AK4" s="12"/>
+    </row>
+    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -658,8 +816,9 @@
       <c r="S5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AK5" s="12"/>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
       <c r="C6">
         <f t="shared" ref="C6:E8" si="0">ROUND(C2*8.2258064516129, 0)</f>
         <v>255</v>
@@ -708,8 +867,9 @@
         <f t="shared" si="3"/>
         <v>58</v>
       </c>
-    </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AK6" s="12"/>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
       <c r="C7">
         <f t="shared" si="0"/>
         <v>255</v>
@@ -758,8 +918,15 @@
         <f t="shared" si="3"/>
         <v>255</v>
       </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="T7" t="s">
+        <v>15</v>
+      </c>
+      <c r="X7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK7" s="12"/>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
       <c r="C8">
         <f t="shared" si="0"/>
         <v>255</v>
@@ -808,19 +975,57 @@
         <f t="shared" si="3"/>
         <v>255</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="S9" s="3">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="S10">
-        <f>T16</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="T8" s="3">
+        <v>20</v>
+      </c>
+      <c r="U8" s="3">
+        <v>1</v>
+      </c>
+      <c r="V8" s="3">
+        <v>20</v>
+      </c>
+      <c r="X8" s="3">
+        <v>48</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>49</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>255</v>
+      </c>
+      <c r="AK8" s="12"/>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="T9">
+        <f>ROUND(T8*8.2258064516129, 0)</f>
+        <v>165</v>
+      </c>
+      <c r="U9">
+        <f>ROUND(U8*8.2258064516129, 0)</f>
+        <v>8</v>
+      </c>
+      <c r="V9">
+        <f>ROUND(V8*8.2258064516129, 0)</f>
+        <v>165</v>
+      </c>
+      <c r="X9">
+        <f>ROUND(X8/8.2258064516129, 0)</f>
+        <v>6</v>
+      </c>
+      <c r="Y9">
+        <f>ROUND(Y8/8.2258064516129, 0)</f>
+        <v>6</v>
+      </c>
+      <c r="Z9">
+        <f>ROUND(Z8/8.2258064516129, 0)</f>
+        <v>31</v>
+      </c>
+      <c r="AK9" s="12"/>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK10" s="12"/>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
@@ -840,7 +1045,7 @@
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
         <v>4</v>
@@ -884,44 +1089,15 @@
       <c r="Q12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="T12">
-        <v>34</v>
-      </c>
-      <c r="U12">
-        <v>177</v>
-      </c>
-      <c r="V12">
-        <v>76</v>
-      </c>
-      <c r="X12" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y12">
-        <v>162</v>
-      </c>
-      <c r="Z12">
-        <v>232</v>
-      </c>
-      <c r="AB12">
-        <v>237</v>
-      </c>
-      <c r="AC12">
-        <v>23</v>
-      </c>
-      <c r="AD12">
-        <v>36</v>
-      </c>
-      <c r="AF12" s="4">
-        <v>58</v>
-      </c>
-      <c r="AG12" s="4">
-        <v>58</v>
-      </c>
-      <c r="AH12" s="4">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="T12" t="s">
+        <v>15</v>
+      </c>
+      <c r="X12" s="12"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
         <v>4</v>
@@ -965,44 +1141,45 @@
       <c r="Q13" s="1">
         <v>31</v>
       </c>
-      <c r="T13" s="1">
-        <v>63</v>
-      </c>
-      <c r="U13" s="1">
-        <v>72</v>
-      </c>
-      <c r="V13" s="1">
-        <v>204</v>
-      </c>
-      <c r="X13">
-        <v>237</v>
-      </c>
-      <c r="Y13">
+      <c r="T13" s="3">
+        <v>31</v>
+      </c>
+      <c r="U13" s="3">
+        <v>22</v>
+      </c>
+      <c r="V13" s="3">
+        <v>10</v>
+      </c>
+      <c r="X13" s="3">
+        <v>29</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>21</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>14</v>
+      </c>
+      <c r="AB13" s="3">
         <v>23</v>
       </c>
-      <c r="Z13">
-        <v>36</v>
-      </c>
-      <c r="AB13">
-        <v>237</v>
-      </c>
-      <c r="AC13">
-        <v>23</v>
-      </c>
-      <c r="AD13">
-        <v>36</v>
-      </c>
-      <c r="AF13">
-        <v>255</v>
-      </c>
-      <c r="AG13">
-        <v>255</v>
-      </c>
-      <c r="AH13">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AC13" s="3">
+        <v>17</v>
+      </c>
+      <c r="AD13" s="3">
+        <v>11</v>
+      </c>
+      <c r="AF13" s="3">
+        <v>6</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="3"/>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
         <v>4</v>
@@ -1046,44 +1223,56 @@
       <c r="Q14" s="1">
         <v>31</v>
       </c>
-      <c r="T14" s="1">
-        <v>63</v>
-      </c>
-      <c r="U14" s="1">
-        <v>72</v>
-      </c>
-      <c r="V14" s="1">
-        <v>204</v>
-      </c>
-      <c r="X14" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y14" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z14" s="4" t="s">
-        <v>5</v>
+      <c r="T14">
+        <f>ROUND(T13*8.2258064516129, 0)</f>
+        <v>255</v>
+      </c>
+      <c r="U14">
+        <f>ROUND(U13*8.2258064516129, 0)</f>
+        <v>181</v>
+      </c>
+      <c r="V14">
+        <f>ROUND(V13*8.2258064516129, 0)</f>
+        <v>82</v>
+      </c>
+      <c r="X14">
+        <f>ROUND(X13*8.2258064516129, 0)</f>
+        <v>239</v>
+      </c>
+      <c r="Y14">
+        <f>ROUND(Y13*8.2258064516129, 0)</f>
+        <v>173</v>
+      </c>
+      <c r="Z14">
+        <f>ROUND(Z13*8.2258064516129, 0)</f>
+        <v>115</v>
       </c>
       <c r="AB14">
-        <v>255</v>
+        <f>ROUND(AB13*8.2258064516129, 0)</f>
+        <v>189</v>
       </c>
       <c r="AC14">
-        <v>255</v>
+        <f>ROUND(AC13*8.2258064516129, 0)</f>
+        <v>140</v>
       </c>
       <c r="AD14">
-        <v>255</v>
+        <f>ROUND(AD13*8.2258064516129, 0)</f>
+        <v>90</v>
       </c>
       <c r="AF14">
-        <v>255</v>
+        <f>ROUND(AF13*8.2258064516129, 0)</f>
+        <v>49</v>
       </c>
       <c r="AG14">
-        <v>255</v>
+        <f>ROUND(AG13*8.2258064516129, 0)</f>
+        <v>0</v>
       </c>
       <c r="AH14">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
+        <f>ROUND(AH13*8.2258064516129, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1102,7 +1291,7 @@
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
       <c r="C16">
         <f t="shared" ref="C16:E18" si="4">ROUND(C12*8.2258064516129, 0)</f>
         <v>255</v>
@@ -1150,57 +1339,6 @@
       <c r="Q16">
         <f t="shared" si="7"/>
         <v>58</v>
-      </c>
-      <c r="T16" s="3">
-        <f>ROUND(T12/8.2258064516129, 0)</f>
-        <v>4</v>
-      </c>
-      <c r="U16" s="3">
-        <f>ROUND(U12/8.2258064516129, 0)</f>
-        <v>22</v>
-      </c>
-      <c r="V16" s="3">
-        <f>ROUND(V12/8.2258064516129, 0)</f>
-        <v>9</v>
-      </c>
-      <c r="W16" s="3"/>
-      <c r="X16" s="3">
-        <f>ROUND(X12/8.2258064516129, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y16" s="3">
-        <f>ROUND(Y12/8.2258064516129, 0)</f>
-        <v>20</v>
-      </c>
-      <c r="Z16" s="3">
-        <f>ROUND(Z12/8.2258064516129, 0)</f>
-        <v>28</v>
-      </c>
-      <c r="AA16" s="3"/>
-      <c r="AB16" s="3">
-        <f>ROUND(AB12/8.2258064516129, 0)</f>
-        <v>29</v>
-      </c>
-      <c r="AC16" s="3">
-        <f>ROUND(AC12/8.2258064516129, 0)</f>
-        <v>3</v>
-      </c>
-      <c r="AD16" s="3">
-        <f>ROUND(AD12/8.2258064516129, 0)</f>
-        <v>4</v>
-      </c>
-      <c r="AE16" s="3"/>
-      <c r="AF16" s="3">
-        <f>ROUND(AF12/8.2258064516129, 0)</f>
-        <v>7</v>
-      </c>
-      <c r="AG16" s="3">
-        <f>ROUND(AG12/8.2258064516129, 0)</f>
-        <v>7</v>
-      </c>
-      <c r="AH16" s="3">
-        <f>ROUND(AH12/8.2258064516129, 0)</f>
-        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:34" x14ac:dyDescent="0.25">
@@ -1252,56 +1390,8 @@
         <f t="shared" si="7"/>
         <v>255</v>
       </c>
-      <c r="T17" s="3">
-        <f>ROUND(T13/8.2258064516129, 0)</f>
-        <v>8</v>
-      </c>
-      <c r="U17" s="3">
-        <f>ROUND(U13/8.2258064516129, 0)</f>
-        <v>9</v>
-      </c>
-      <c r="V17" s="3">
-        <f>ROUND(V13/8.2258064516129, 0)</f>
-        <v>25</v>
-      </c>
-      <c r="W17" s="3"/>
-      <c r="X17" s="3">
-        <f>ROUND(X13/8.2258064516129, 0)</f>
-        <v>29</v>
-      </c>
-      <c r="Y17" s="3">
-        <f>ROUND(Y13/8.2258064516129, 0)</f>
-        <v>3</v>
-      </c>
-      <c r="Z17" s="3">
-        <f>ROUND(Z13/8.2258064516129, 0)</f>
-        <v>4</v>
-      </c>
-      <c r="AA17" s="3"/>
-      <c r="AB17" s="3">
-        <f>ROUND(AB13/8.2258064516129, 0)</f>
-        <v>29</v>
-      </c>
-      <c r="AC17" s="3">
-        <f>ROUND(AC13/8.2258064516129, 0)</f>
-        <v>3</v>
-      </c>
-      <c r="AD17" s="3">
-        <f>ROUND(AD13/8.2258064516129, 0)</f>
-        <v>4</v>
-      </c>
-      <c r="AE17" s="3"/>
-      <c r="AF17" s="3">
-        <f>ROUND(AF13/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="AG17" s="3">
-        <f>ROUND(AG13/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="AH17" s="3">
-        <f>ROUND(AH13/8.2258064516129, 0)</f>
-        <v>31</v>
+      <c r="T17" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.25">
@@ -1354,55 +1444,84 @@
         <v>255</v>
       </c>
       <c r="T18" s="3">
-        <f>ROUND(T14/8.2258064516129, 0)</f>
-        <v>8</v>
+        <v>255</v>
       </c>
       <c r="U18" s="3">
-        <f>ROUND(U14/8.2258064516129, 0)</f>
-        <v>9</v>
+        <v>178</v>
       </c>
       <c r="V18" s="3">
-        <f>ROUND(V14/8.2258064516129, 0)</f>
-        <v>25</v>
-      </c>
-      <c r="W18" s="3"/>
+        <v>82</v>
+      </c>
       <c r="X18" s="3">
-        <f>ROUND(X14/8.2258064516129, 0)</f>
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="Y18" s="3">
-        <f>ROUND(Y14/8.2258064516129, 0)</f>
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="Z18" s="3">
-        <f>ROUND(Z14/8.2258064516129, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="AA18" s="3"/>
+        <v>115</v>
+      </c>
       <c r="AB18" s="3">
-        <f>ROUND(AB14/8.2258064516129, 0)</f>
-        <v>31</v>
+        <v>189</v>
       </c>
       <c r="AC18" s="3">
-        <f>ROUND(AC14/8.2258064516129, 0)</f>
-        <v>31</v>
+        <v>137</v>
       </c>
       <c r="AD18" s="3">
-        <f>ROUND(AD14/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="AE18" s="3"/>
-      <c r="AF18" s="3">
-        <f>ROUND(AF14/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="AG18" s="3">
-        <f>ROUND(AG14/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="AH18" s="3">
-        <f>ROUND(AH14/8.2258064516129, 0)</f>
-        <v>31</v>
+        <v>91</v>
+      </c>
+      <c r="AF18" s="3"/>
+      <c r="AG18" s="3"/>
+      <c r="AH18" s="3"/>
+    </row>
+    <row r="19" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="T19">
+        <f>ROUND(T18/8.2258064516129, 0)</f>
+        <v>31</v>
+      </c>
+      <c r="U19">
+        <f>ROUND(U18/8.2258064516129, 0)</f>
+        <v>22</v>
+      </c>
+      <c r="V19">
+        <f>ROUND(V18/8.2258064516129, 0)</f>
+        <v>10</v>
+      </c>
+      <c r="X19">
+        <f>ROUND(X18/8.2258064516129, 0)</f>
+        <v>29</v>
+      </c>
+      <c r="Y19">
+        <f>ROUND(Y18/8.2258064516129, 0)</f>
+        <v>21</v>
+      </c>
+      <c r="Z19">
+        <f>ROUND(Z18/8.2258064516129, 0)</f>
+        <v>14</v>
+      </c>
+      <c r="AB19">
+        <f>ROUND(AB18/8.2258064516129, 0)</f>
+        <v>23</v>
+      </c>
+      <c r="AC19">
+        <f>ROUND(AC18/8.2258064516129, 0)</f>
+        <v>17</v>
+      </c>
+      <c r="AD19">
+        <f>ROUND(AD18/8.2258064516129, 0)</f>
+        <v>11</v>
+      </c>
+      <c r="AF19">
+        <f>ROUND(AF18/8.2258064516129, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <f>ROUND(AG18/8.2258064516129, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH19">
+        <f>ROUND(AH18/8.2258064516129, 0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:34" x14ac:dyDescent="0.25">
@@ -1469,42 +1588,12 @@
       <c r="Q22" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="T22">
-        <v>255</v>
-      </c>
-      <c r="U22">
-        <v>201</v>
-      </c>
-      <c r="V22">
-        <v>14</v>
-      </c>
-      <c r="X22">
-        <v>255</v>
-      </c>
-      <c r="Y22">
-        <v>72</v>
-      </c>
-      <c r="Z22">
-        <v>16</v>
-      </c>
-      <c r="AB22" s="1">
-        <v>63</v>
-      </c>
-      <c r="AC22" s="1">
-        <v>72</v>
-      </c>
-      <c r="AD22" s="1">
-        <v>204</v>
-      </c>
-      <c r="AF22" s="4">
-        <v>58</v>
-      </c>
-      <c r="AG22" s="4">
-        <v>58</v>
-      </c>
-      <c r="AH22" s="4">
-        <v>58</v>
-      </c>
+      <c r="AB22" s="1"/>
+      <c r="AC22" s="1"/>
+      <c r="AD22" s="1"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
     </row>
     <row r="23" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
@@ -1550,42 +1639,12 @@
       <c r="Q23" s="1">
         <v>31</v>
       </c>
-      <c r="T23">
-        <v>255</v>
-      </c>
-      <c r="U23">
-        <v>72</v>
-      </c>
-      <c r="V23">
-        <v>16</v>
-      </c>
-      <c r="X23" s="1">
-        <v>63</v>
-      </c>
-      <c r="Y23" s="1">
-        <v>72</v>
-      </c>
-      <c r="Z23" s="1">
-        <v>204</v>
-      </c>
-      <c r="AB23" s="1">
-        <v>63</v>
-      </c>
-      <c r="AC23" s="1">
-        <v>72</v>
-      </c>
-      <c r="AD23" s="1">
-        <v>204</v>
-      </c>
-      <c r="AF23">
-        <v>255</v>
-      </c>
-      <c r="AG23">
-        <v>255</v>
-      </c>
-      <c r="AH23">
-        <v>255</v>
-      </c>
+      <c r="X23" s="1"/>
+      <c r="Y23" s="1"/>
+      <c r="Z23" s="1"/>
+      <c r="AB23" s="1"/>
+      <c r="AC23" s="1"/>
+      <c r="AD23" s="1"/>
     </row>
     <row r="24" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
@@ -1631,42 +1690,9 @@
       <c r="Q24" s="1">
         <v>31</v>
       </c>
-      <c r="T24">
-        <v>255</v>
-      </c>
-      <c r="U24">
-        <v>72</v>
-      </c>
-      <c r="V24">
-        <v>16</v>
-      </c>
-      <c r="X24" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y24" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z24" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB24">
-        <v>255</v>
-      </c>
-      <c r="AC24">
-        <v>255</v>
-      </c>
-      <c r="AD24">
-        <v>255</v>
-      </c>
-      <c r="AF24">
-        <v>255</v>
-      </c>
-      <c r="AG24">
-        <v>255</v>
-      </c>
-      <c r="AH24">
-        <v>255</v>
-      </c>
+      <c r="X24" s="12"/>
+      <c r="Y24" s="12"/>
+      <c r="Z24" s="12"/>
     </row>
     <row r="25" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
@@ -1736,57 +1762,6 @@
         <f t="shared" si="11"/>
         <v>58</v>
       </c>
-      <c r="T26" s="3">
-        <f>ROUND(T22/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="U26" s="3">
-        <f>ROUND(U22/8.2258064516129, 0)</f>
-        <v>24</v>
-      </c>
-      <c r="V26" s="3">
-        <f>ROUND(V22/8.2258064516129, 0)</f>
-        <v>2</v>
-      </c>
-      <c r="W26" s="3"/>
-      <c r="X26" s="3">
-        <f>ROUND(X22/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="Y26" s="3">
-        <f>ROUND(Y22/8.2258064516129, 0)</f>
-        <v>9</v>
-      </c>
-      <c r="Z26" s="3">
-        <f>ROUND(Z22/8.2258064516129, 0)</f>
-        <v>2</v>
-      </c>
-      <c r="AA26" s="3"/>
-      <c r="AB26" s="3">
-        <f>ROUND(AB22/8.2258064516129, 0)</f>
-        <v>8</v>
-      </c>
-      <c r="AC26" s="3">
-        <f>ROUND(AC22/8.2258064516129, 0)</f>
-        <v>9</v>
-      </c>
-      <c r="AD26" s="3">
-        <f>ROUND(AD22/8.2258064516129, 0)</f>
-        <v>25</v>
-      </c>
-      <c r="AE26" s="3"/>
-      <c r="AF26" s="3">
-        <f>ROUND(AF22/8.2258064516129, 0)</f>
-        <v>7</v>
-      </c>
-      <c r="AG26" s="3">
-        <f>ROUND(AG22/8.2258064516129, 0)</f>
-        <v>7</v>
-      </c>
-      <c r="AH26" s="3">
-        <f>ROUND(AH22/8.2258064516129, 0)</f>
-        <v>7</v>
-      </c>
     </row>
     <row r="27" spans="1:34" x14ac:dyDescent="0.25">
       <c r="C27">
@@ -1837,57 +1812,6 @@
         <f t="shared" si="11"/>
         <v>255</v>
       </c>
-      <c r="T27" s="3">
-        <f>ROUND(T23/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="U27" s="3">
-        <f>ROUND(U23/8.2258064516129, 0)</f>
-        <v>9</v>
-      </c>
-      <c r="V27" s="3">
-        <f>ROUND(V23/8.2258064516129, 0)</f>
-        <v>2</v>
-      </c>
-      <c r="W27" s="3"/>
-      <c r="X27" s="3">
-        <f>ROUND(X23/8.2258064516129, 0)</f>
-        <v>8</v>
-      </c>
-      <c r="Y27" s="3">
-        <f>ROUND(Y23/8.2258064516129, 0)</f>
-        <v>9</v>
-      </c>
-      <c r="Z27" s="3">
-        <f>ROUND(Z23/8.2258064516129, 0)</f>
-        <v>25</v>
-      </c>
-      <c r="AA27" s="3"/>
-      <c r="AB27" s="3">
-        <f>ROUND(AB23/8.2258064516129, 0)</f>
-        <v>8</v>
-      </c>
-      <c r="AC27" s="3">
-        <f>ROUND(AC23/8.2258064516129, 0)</f>
-        <v>9</v>
-      </c>
-      <c r="AD27" s="3">
-        <f>ROUND(AD23/8.2258064516129, 0)</f>
-        <v>25</v>
-      </c>
-      <c r="AE27" s="3"/>
-      <c r="AF27" s="3">
-        <f>ROUND(AF23/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="AG27" s="3">
-        <f>ROUND(AG23/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="AH27" s="3">
-        <f>ROUND(AH23/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
     </row>
     <row r="28" spans="1:34" x14ac:dyDescent="0.25">
       <c r="C28">
@@ -1937,57 +1861,6 @@
       <c r="Q28">
         <f t="shared" si="11"/>
         <v>255</v>
-      </c>
-      <c r="T28" s="3">
-        <f>ROUND(T24/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="U28" s="3">
-        <f>ROUND(U24/8.2258064516129, 0)</f>
-        <v>9</v>
-      </c>
-      <c r="V28" s="3">
-        <f>ROUND(V24/8.2258064516129, 0)</f>
-        <v>2</v>
-      </c>
-      <c r="W28" s="3"/>
-      <c r="X28" s="3">
-        <f>ROUND(X24/8.2258064516129, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y28" s="3">
-        <f>ROUND(Y24/8.2258064516129, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="Z28" s="3">
-        <f>ROUND(Z24/8.2258064516129, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="AA28" s="3"/>
-      <c r="AB28" s="3">
-        <f>ROUND(AB24/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="AC28" s="3">
-        <f>ROUND(AC24/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="AD28" s="3">
-        <f>ROUND(AD24/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="AE28" s="3"/>
-      <c r="AF28" s="3">
-        <f>ROUND(AF24/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="AG28" s="3">
-        <f>ROUND(AG24/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="AH28" s="3">
-        <f>ROUND(AH24/8.2258064516129, 0)</f>
-        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:34" x14ac:dyDescent="0.25">
@@ -2054,42 +1927,9 @@
       <c r="Q32" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="T32">
-        <v>136</v>
-      </c>
-      <c r="U32">
-        <v>0</v>
-      </c>
-      <c r="V32">
-        <v>21</v>
-      </c>
-      <c r="X32">
-        <v>0</v>
-      </c>
-      <c r="Y32">
-        <v>162</v>
-      </c>
-      <c r="Z32">
-        <v>232</v>
-      </c>
-      <c r="AB32">
-        <v>255</v>
-      </c>
-      <c r="AC32">
-        <v>201</v>
-      </c>
-      <c r="AD32">
-        <v>14</v>
-      </c>
-      <c r="AF32" s="4">
-        <v>58</v>
-      </c>
-      <c r="AG32" s="4">
-        <v>58</v>
-      </c>
-      <c r="AH32" s="4">
-        <v>58</v>
-      </c>
+      <c r="AF32" s="12"/>
+      <c r="AG32" s="12"/>
+      <c r="AH32" s="12"/>
     </row>
     <row r="33" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
@@ -2135,42 +1975,9 @@
       <c r="Q33" s="1">
         <v>31</v>
       </c>
-      <c r="T33" s="1">
-        <v>34</v>
-      </c>
-      <c r="U33" s="1">
-        <v>177</v>
-      </c>
-      <c r="V33" s="1">
-        <v>76</v>
-      </c>
-      <c r="X33">
-        <v>255</v>
-      </c>
-      <c r="Y33">
-        <v>201</v>
-      </c>
-      <c r="Z33">
-        <v>14</v>
-      </c>
-      <c r="AB33">
-        <v>255</v>
-      </c>
-      <c r="AC33">
-        <v>201</v>
-      </c>
-      <c r="AD33">
-        <v>14</v>
-      </c>
-      <c r="AF33">
-        <v>255</v>
-      </c>
-      <c r="AG33">
-        <v>255</v>
-      </c>
-      <c r="AH33">
-        <v>255</v>
-      </c>
+      <c r="T33" s="1"/>
+      <c r="U33" s="1"/>
+      <c r="V33" s="1"/>
     </row>
     <row r="34" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
@@ -2216,42 +2023,12 @@
       <c r="Q34" s="1">
         <v>31</v>
       </c>
-      <c r="T34" s="1">
-        <v>34</v>
-      </c>
-      <c r="U34" s="1">
-        <v>177</v>
-      </c>
-      <c r="V34" s="1">
-        <v>76</v>
-      </c>
-      <c r="X34" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y34" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z34" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB34">
-        <v>255</v>
-      </c>
-      <c r="AC34">
-        <v>255</v>
-      </c>
-      <c r="AD34">
-        <v>255</v>
-      </c>
-      <c r="AF34">
-        <v>255</v>
-      </c>
-      <c r="AG34">
-        <v>255</v>
-      </c>
-      <c r="AH34">
-        <v>255</v>
-      </c>
+      <c r="T34" s="1"/>
+      <c r="U34" s="1"/>
+      <c r="V34" s="1"/>
+      <c r="X34" s="12"/>
+      <c r="Y34" s="12"/>
+      <c r="Z34" s="12"/>
     </row>
     <row r="36" spans="1:34" x14ac:dyDescent="0.25">
       <c r="C36">
@@ -2302,57 +2079,6 @@
         <f t="shared" si="15"/>
         <v>58</v>
       </c>
-      <c r="T36" s="3">
-        <f>ROUND(T32/8.2258064516129, 0)</f>
-        <v>17</v>
-      </c>
-      <c r="U36" s="3">
-        <f>ROUND(U32/8.2258064516129, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V36" s="3">
-        <f>ROUND(V32/8.2258064516129, 0)</f>
-        <v>3</v>
-      </c>
-      <c r="W36" s="3"/>
-      <c r="X36" s="3">
-        <f>ROUND(X32/8.2258064516129, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y36" s="3">
-        <f>ROUND(Y32/8.2258064516129, 0)</f>
-        <v>20</v>
-      </c>
-      <c r="Z36" s="3">
-        <f>ROUND(Z32/8.2258064516129, 0)</f>
-        <v>28</v>
-      </c>
-      <c r="AA36" s="3"/>
-      <c r="AB36" s="3">
-        <f>ROUND(AB32/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="AC36" s="3">
-        <f>ROUND(AC32/8.2258064516129, 0)</f>
-        <v>24</v>
-      </c>
-      <c r="AD36" s="3">
-        <f>ROUND(AD32/8.2258064516129, 0)</f>
-        <v>2</v>
-      </c>
-      <c r="AE36" s="3"/>
-      <c r="AF36" s="3">
-        <f>ROUND(AF32/8.2258064516129, 0)</f>
-        <v>7</v>
-      </c>
-      <c r="AG36" s="3">
-        <f>ROUND(AG32/8.2258064516129, 0)</f>
-        <v>7</v>
-      </c>
-      <c r="AH36" s="3">
-        <f>ROUND(AH32/8.2258064516129, 0)</f>
-        <v>7</v>
-      </c>
     </row>
     <row r="37" spans="1:34" x14ac:dyDescent="0.25">
       <c r="C37">
@@ -2403,57 +2129,6 @@
         <f t="shared" si="15"/>
         <v>255</v>
       </c>
-      <c r="T37" s="3">
-        <f>ROUND(T33/8.2258064516129, 0)</f>
-        <v>4</v>
-      </c>
-      <c r="U37" s="3">
-        <f>ROUND(U33/8.2258064516129, 0)</f>
-        <v>22</v>
-      </c>
-      <c r="V37" s="3">
-        <f>ROUND(V33/8.2258064516129, 0)</f>
-        <v>9</v>
-      </c>
-      <c r="W37" s="3"/>
-      <c r="X37" s="3">
-        <f>ROUND(X33/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="Y37" s="3">
-        <f>ROUND(Y33/8.2258064516129, 0)</f>
-        <v>24</v>
-      </c>
-      <c r="Z37" s="3">
-        <f>ROUND(Z33/8.2258064516129, 0)</f>
-        <v>2</v>
-      </c>
-      <c r="AA37" s="3"/>
-      <c r="AB37" s="3">
-        <f>ROUND(AB33/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="AC37" s="3">
-        <f>ROUND(AC33/8.2258064516129, 0)</f>
-        <v>24</v>
-      </c>
-      <c r="AD37" s="3">
-        <f>ROUND(AD33/8.2258064516129, 0)</f>
-        <v>2</v>
-      </c>
-      <c r="AE37" s="3"/>
-      <c r="AF37" s="3">
-        <f>ROUND(AF33/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="AG37" s="3">
-        <f>ROUND(AG33/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="AH37" s="3">
-        <f>ROUND(AH33/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
     </row>
     <row r="38" spans="1:34" x14ac:dyDescent="0.25">
       <c r="C38">
@@ -2504,330 +2179,3916 @@
         <f t="shared" si="15"/>
         <v>255</v>
       </c>
-      <c r="T38" s="3">
-        <f>ROUND(T34/8.2258064516129, 0)</f>
+    </row>
+    <row r="42" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AF42" s="12"/>
+      <c r="AG42" s="12"/>
+      <c r="AH42" s="12"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{177AA22C-2659-41FE-BD81-E14E7A764E95}">
+  <dimension ref="A1:AJ55"/>
+  <sheetFormatPr defaultColWidth="4.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="21" width="4.7109375" style="13"/>
+    <col min="22" max="22" width="4.7109375" style="13" customWidth="1"/>
+    <col min="23" max="16384" width="4.7109375" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="U38" s="3">
-        <f>ROUND(U34/8.2258064516129, 0)</f>
+      <c r="B2" s="4">
+        <f t="shared" ref="B2:B13" si="0">ROUND(T2/8.2258064516129, 0)</f>
+        <v>28</v>
+      </c>
+      <c r="C2" s="4">
+        <f t="shared" ref="C2:C13" si="1">ROUND(U2/8.2258064516129, 0)</f>
+        <v>31</v>
+      </c>
+      <c r="D2" s="4">
+        <f t="shared" ref="D2:D13" si="2">ROUND(V2/8.2258064516129, 0)</f>
+        <v>16</v>
+      </c>
+      <c r="E2" s="13"/>
+      <c r="F2" s="4">
+        <f t="shared" ref="F2:F13" si="3">ROUND(X2/8.2258064516129, 0)</f>
+        <v>31</v>
+      </c>
+      <c r="G2" s="4">
+        <f t="shared" ref="G2:G13" si="4">ROUND(Y2/8.2258064516129, 0)</f>
         <v>22</v>
       </c>
-      <c r="V38" s="3">
-        <f>ROUND(V34/8.2258064516129, 0)</f>
+      <c r="H2" s="4">
+        <f t="shared" ref="H2:H13" si="5">ROUND(Z2/8.2258064516129, 0)</f>
+        <v>10</v>
+      </c>
+      <c r="I2" s="13"/>
+      <c r="J2" s="4">
+        <f t="shared" ref="J2:J13" si="6">ROUND(AB2/8.2258064516129, 0)</f>
+        <v>31</v>
+      </c>
+      <c r="K2" s="4">
+        <f t="shared" ref="K2:K13" si="7">ROUND(AC2/8.2258064516129, 0)</f>
+        <v>7</v>
+      </c>
+      <c r="L2" s="4">
+        <f t="shared" ref="L2:L13" si="8">ROUND(AD2/8.2258064516129, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="M2" s="13"/>
+      <c r="N2" s="4">
+        <f t="shared" ref="N2:N13" si="9">ROUND(AF2/8.2258064516129, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="O2" s="4">
+        <f t="shared" ref="O2:O13" si="10">ROUND(AG2/8.2258064516129, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="P2" s="4">
+        <f t="shared" ref="P2:P13" si="11">ROUND(AH2/8.2258064516129, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="S2" s="13"/>
+      <c r="T2" s="4">
+        <v>230</v>
+      </c>
+      <c r="U2" s="4">
+        <v>255</v>
+      </c>
+      <c r="V2" s="4">
+        <v>132</v>
+      </c>
+      <c r="W2" s="13"/>
+      <c r="X2" s="4">
+        <v>255</v>
+      </c>
+      <c r="Y2" s="4">
+        <v>178</v>
+      </c>
+      <c r="Z2" s="4">
+        <v>82</v>
+      </c>
+      <c r="AA2" s="13"/>
+      <c r="AB2" s="4">
+        <v>255</v>
+      </c>
+      <c r="AC2" s="4">
+        <v>58</v>
+      </c>
+      <c r="AD2" s="4">
+        <v>8</v>
+      </c>
+      <c r="AE2" s="13"/>
+      <c r="AI2" s="13"/>
+      <c r="AJ2" s="13"/>
+    </row>
+    <row r="3" spans="1:36" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="14">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C3" s="14">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="D3" s="14">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="E3" s="13"/>
+      <c r="F3" s="14">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="G3" s="14">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="H3" s="14">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="I3" s="13"/>
+      <c r="J3" s="14">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="K3" s="14">
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
-      <c r="W38" s="3"/>
-      <c r="X38" s="3">
-        <f>ROUND(X34/8.2258064516129, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="Y38" s="3">
-        <f>ROUND(Y34/8.2258064516129, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="Z38" s="3">
-        <f>ROUND(Z34/8.2258064516129, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="AA38" s="3"/>
-      <c r="AB38" s="3">
-        <f>ROUND(AB34/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="AC38" s="3">
-        <f>ROUND(AC34/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="AD38" s="3">
-        <f>ROUND(AD34/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="AE38" s="3"/>
-      <c r="AF38" s="3">
-        <f>ROUND(AF34/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="AG38" s="3">
-        <f>ROUND(AG34/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="AH38" s="3">
-        <f>ROUND(AH34/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="42" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="T42">
-        <v>237</v>
-      </c>
-      <c r="U42">
+      <c r="L3" s="14">
+        <f t="shared" si="8"/>
+        <v>31</v>
+      </c>
+      <c r="M3" s="13"/>
+      <c r="N3" s="14">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O3" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P3" s="14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="S3" s="13"/>
+      <c r="T3" s="14">
+        <v>230</v>
+      </c>
+      <c r="U3" s="14">
+        <v>255</v>
+      </c>
+      <c r="V3" s="14">
+        <v>132</v>
+      </c>
+      <c r="W3" s="13"/>
+      <c r="X3" s="14">
+        <v>255</v>
+      </c>
+      <c r="Y3" s="14">
+        <v>178</v>
+      </c>
+      <c r="Z3" s="14">
+        <v>82</v>
+      </c>
+      <c r="AA3" s="13"/>
+      <c r="AB3" s="14">
+        <v>82</v>
+      </c>
+      <c r="AC3" s="14">
+        <v>74</v>
+      </c>
+      <c r="AD3" s="14">
+        <v>255</v>
+      </c>
+      <c r="AE3" s="13"/>
+      <c r="AI3" s="13"/>
+      <c r="AJ3" s="13"/>
+    </row>
+    <row r="4" spans="1:36" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="5">
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="V42">
-        <v>36</v>
-      </c>
-      <c r="X42">
-        <v>255</v>
-      </c>
-      <c r="Y42">
-        <v>201</v>
-      </c>
-      <c r="Z42">
+      <c r="C4" s="5">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="D4" s="5">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="E4" s="13"/>
+      <c r="F4" s="5">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="G4" s="5">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="H4" s="5">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="I4" s="13"/>
+      <c r="J4" s="5">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="K4" s="5">
+        <f t="shared" si="7"/>
+        <v>23</v>
+      </c>
+      <c r="L4" s="5">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="M4" s="13"/>
+      <c r="N4" s="5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O4" s="5">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P4" s="5">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="S4" s="13"/>
+      <c r="T4" s="5">
+        <v>230</v>
+      </c>
+      <c r="U4" s="5">
+        <v>255</v>
+      </c>
+      <c r="V4" s="5">
+        <v>132</v>
+      </c>
+      <c r="W4" s="13"/>
+      <c r="X4" s="5">
+        <v>255</v>
+      </c>
+      <c r="Y4" s="5">
+        <v>178</v>
+      </c>
+      <c r="Z4" s="5">
+        <v>82</v>
+      </c>
+      <c r="AA4" s="13"/>
+      <c r="AB4" s="5">
+        <v>58</v>
+      </c>
+      <c r="AC4" s="5">
+        <v>189</v>
+      </c>
+      <c r="AD4" s="5">
+        <v>25</v>
+      </c>
+      <c r="AE4" s="13"/>
+      <c r="AI4" s="13"/>
+      <c r="AJ4" s="13"/>
+    </row>
+    <row r="5" spans="1:36" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C5" s="7">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="D5" s="7">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="E5" s="13"/>
+      <c r="F5" s="7">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="G5" s="7">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="H5" s="7">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="I5" s="13"/>
+      <c r="J5" s="7">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="K5" s="7">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+      <c r="L5" s="7">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="M5" s="13"/>
+      <c r="N5" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O5" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P5" s="7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="S5" s="13"/>
+      <c r="T5" s="7">
+        <v>230</v>
+      </c>
+      <c r="U5" s="7">
+        <v>255</v>
+      </c>
+      <c r="V5" s="7">
+        <v>132</v>
+      </c>
+      <c r="W5" s="13"/>
+      <c r="X5" s="7">
+        <v>255</v>
+      </c>
+      <c r="Y5" s="7">
+        <v>178</v>
+      </c>
+      <c r="Z5" s="7">
+        <v>82</v>
+      </c>
+      <c r="AA5" s="13"/>
+      <c r="AB5" s="7">
+        <v>123</v>
+      </c>
+      <c r="AC5" s="7">
+        <v>82</v>
+      </c>
+      <c r="AD5" s="7">
+        <v>25</v>
+      </c>
+      <c r="AE5" s="13"/>
+      <c r="AI5" s="13"/>
+      <c r="AJ5" s="13"/>
+    </row>
+    <row r="6" spans="1:36" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="16">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C6" s="16">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="D6" s="16">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="E6" s="13"/>
+      <c r="F6" s="16">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="G6" s="16">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="H6" s="16">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="I6" s="13"/>
+      <c r="J6" s="16">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+      <c r="K6" s="16">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="L6" s="16">
+        <f t="shared" si="8"/>
+        <v>20</v>
+      </c>
+      <c r="M6" s="13"/>
+      <c r="N6" s="16">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O6" s="16">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P6" s="16">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="S6" s="13"/>
+      <c r="T6" s="16">
+        <v>230</v>
+      </c>
+      <c r="U6" s="16">
+        <v>255</v>
+      </c>
+      <c r="V6" s="16">
+        <v>132</v>
+      </c>
+      <c r="W6" s="13"/>
+      <c r="X6" s="16">
+        <v>255</v>
+      </c>
+      <c r="Y6" s="16">
+        <v>178</v>
+      </c>
+      <c r="Z6" s="16">
+        <v>82</v>
+      </c>
+      <c r="AA6" s="13"/>
+      <c r="AB6" s="16">
+        <v>165</v>
+      </c>
+      <c r="AC6" s="16">
+        <v>8</v>
+      </c>
+      <c r="AD6" s="16">
+        <v>165</v>
+      </c>
+      <c r="AE6" s="13"/>
+      <c r="AI6" s="13"/>
+      <c r="AJ6" s="13"/>
+    </row>
+    <row r="7" spans="1:36" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="6">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C7" s="6">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="D7" s="6">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="E7" s="13"/>
+      <c r="F7" s="6">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="G7" s="6">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="H7" s="6">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="I7" s="13"/>
+      <c r="J7" s="6">
+        <f t="shared" si="6"/>
+        <v>23</v>
+      </c>
+      <c r="K7" s="6">
+        <f t="shared" si="7"/>
+        <v>23</v>
+      </c>
+      <c r="L7" s="6">
+        <f t="shared" si="8"/>
+        <v>23</v>
+      </c>
+      <c r="M7" s="13"/>
+      <c r="N7" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O7" s="6">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P7" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="S7" s="13"/>
+      <c r="T7" s="6">
+        <v>230</v>
+      </c>
+      <c r="U7" s="6">
+        <v>255</v>
+      </c>
+      <c r="V7" s="6">
+        <v>132</v>
+      </c>
+      <c r="W7" s="13"/>
+      <c r="X7" s="6">
+        <v>255</v>
+      </c>
+      <c r="Y7" s="6">
+        <v>178</v>
+      </c>
+      <c r="Z7" s="6">
+        <v>82</v>
+      </c>
+      <c r="AA7" s="13"/>
+      <c r="AB7" s="6">
+        <v>191</v>
+      </c>
+      <c r="AC7" s="6">
+        <v>191</v>
+      </c>
+      <c r="AD7" s="6">
+        <v>191</v>
+      </c>
+      <c r="AE7" s="13"/>
+      <c r="AI7" s="13"/>
+      <c r="AJ7" s="13"/>
+    </row>
+    <row r="8" spans="1:36" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="8">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C8" s="8">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="D8" s="8">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="E8" s="13"/>
+      <c r="F8" s="8">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="G8" s="8">
+        <f t="shared" si="4"/>
+        <v>25</v>
+      </c>
+      <c r="H8" s="8">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="I8" s="13"/>
+      <c r="J8" s="8">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="K8" s="8">
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
-      <c r="AB42">
-        <v>34</v>
-      </c>
-      <c r="AC42">
-        <v>177</v>
-      </c>
-      <c r="AD42">
-        <v>76</v>
-      </c>
-      <c r="AF42" s="4">
+      <c r="L8" s="8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M8" s="13"/>
+      <c r="N8" s="8">
+        <f t="shared" si="9"/>
+        <v>7</v>
+      </c>
+      <c r="O8" s="8">
+        <f t="shared" si="10"/>
+        <v>7</v>
+      </c>
+      <c r="P8" s="8">
+        <f t="shared" si="11"/>
+        <v>7</v>
+      </c>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="S8" s="13"/>
+      <c r="T8" s="8">
+        <v>230</v>
+      </c>
+      <c r="U8" s="8">
+        <v>255</v>
+      </c>
+      <c r="V8" s="8">
+        <v>132</v>
+      </c>
+      <c r="W8" s="13"/>
+      <c r="X8" s="8">
+        <v>99</v>
+      </c>
+      <c r="Y8" s="8">
+        <v>206</v>
+      </c>
+      <c r="Z8" s="8">
+        <v>8</v>
+      </c>
+      <c r="AA8" s="13"/>
+      <c r="AB8" s="8">
+        <v>41</v>
+      </c>
+      <c r="AC8" s="8">
+        <v>115</v>
+      </c>
+      <c r="AD8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="13"/>
+      <c r="AF8" s="8">
         <v>58</v>
       </c>
-      <c r="AG42" s="4">
+      <c r="AG8" s="8">
         <v>58</v>
       </c>
-      <c r="AH42" s="4">
+      <c r="AH8" s="8">
         <v>58</v>
       </c>
-    </row>
-    <row r="43" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="T43">
-        <v>255</v>
-      </c>
-      <c r="U43">
-        <v>72</v>
-      </c>
-      <c r="V43">
+      <c r="AI8" s="13"/>
+      <c r="AJ8" s="13"/>
+    </row>
+    <row r="9" spans="1:36" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="7">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C9" s="7">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="D9" s="7">
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="X43">
-        <v>34</v>
-      </c>
-      <c r="Y43">
-        <v>177</v>
-      </c>
-      <c r="Z43">
-        <v>76</v>
-      </c>
-      <c r="AB43">
-        <v>34</v>
-      </c>
-      <c r="AC43">
-        <v>177</v>
-      </c>
-      <c r="AD43">
-        <v>76</v>
-      </c>
-      <c r="AF43">
-        <v>255</v>
-      </c>
-      <c r="AG43">
-        <v>255</v>
-      </c>
-      <c r="AH43">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="44" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="T44">
-        <v>255</v>
-      </c>
-      <c r="U44">
-        <v>72</v>
-      </c>
-      <c r="V44">
+      <c r="E9" s="13"/>
+      <c r="F9" s="7">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="G9" s="7">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="H9" s="7">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="I9" s="13"/>
+      <c r="J9" s="7">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="K9" s="7">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+      <c r="L9" s="7">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="M9" s="13"/>
+      <c r="N9" s="7">
+        <f t="shared" si="9"/>
+        <v>7</v>
+      </c>
+      <c r="O9" s="7">
+        <f t="shared" si="10"/>
+        <v>7</v>
+      </c>
+      <c r="P9" s="7">
+        <f t="shared" si="11"/>
+        <v>7</v>
+      </c>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="S9" s="13"/>
+      <c r="T9" s="7">
+        <v>230</v>
+      </c>
+      <c r="U9" s="7">
+        <v>255</v>
+      </c>
+      <c r="V9" s="7">
+        <v>132</v>
+      </c>
+      <c r="W9" s="13"/>
+      <c r="X9" s="7">
+        <v>197</v>
+      </c>
+      <c r="Y9" s="7">
+        <v>148</v>
+      </c>
+      <c r="Z9" s="7">
+        <v>58</v>
+      </c>
+      <c r="AA9" s="13"/>
+      <c r="AB9" s="7">
+        <v>123</v>
+      </c>
+      <c r="AC9" s="7">
+        <v>82</v>
+      </c>
+      <c r="AD9" s="7">
+        <v>25</v>
+      </c>
+      <c r="AE9" s="13"/>
+      <c r="AF9" s="7">
+        <v>58</v>
+      </c>
+      <c r="AG9" s="7">
+        <v>58</v>
+      </c>
+      <c r="AH9" s="7">
+        <v>58</v>
+      </c>
+      <c r="AI9" s="13"/>
+      <c r="AJ9" s="13"/>
+    </row>
+    <row r="10" spans="1:36" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="9">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C10" s="9">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="D10" s="9">
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="X44">
-        <v>255</v>
-      </c>
-      <c r="Y44">
-        <v>255</v>
-      </c>
-      <c r="Z44">
-        <v>255</v>
-      </c>
-      <c r="AB44">
-        <v>255</v>
-      </c>
-      <c r="AC44">
-        <v>255</v>
-      </c>
-      <c r="AD44">
-        <v>255</v>
-      </c>
-      <c r="AF44">
-        <v>255</v>
-      </c>
-      <c r="AG44">
-        <v>255</v>
-      </c>
-      <c r="AH44">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="46" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="T46" s="3">
-        <f>ROUND(T42/8.2258064516129, 0)</f>
+      <c r="E10" s="13"/>
+      <c r="F10" s="9">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="G10" s="9">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="H10" s="9">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="I10" s="13"/>
+      <c r="J10" s="9">
+        <f t="shared" si="6"/>
+        <v>27</v>
+      </c>
+      <c r="K10" s="9">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="L10" s="9">
+        <f t="shared" si="8"/>
+        <v>16</v>
+      </c>
+      <c r="M10" s="13"/>
+      <c r="N10" s="9">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O10" s="9">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P10" s="9">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="S10" s="13"/>
+      <c r="T10" s="9">
+        <v>230</v>
+      </c>
+      <c r="U10" s="9">
+        <v>255</v>
+      </c>
+      <c r="V10" s="9">
+        <v>132</v>
+      </c>
+      <c r="W10" s="13"/>
+      <c r="X10" s="9">
+        <v>255</v>
+      </c>
+      <c r="Y10" s="9">
+        <v>178</v>
+      </c>
+      <c r="Z10" s="9">
+        <v>82</v>
+      </c>
+      <c r="AA10" s="13"/>
+      <c r="AB10" s="9">
+        <v>222</v>
+      </c>
+      <c r="AC10" s="9">
+        <v>58</v>
+      </c>
+      <c r="AD10" s="9">
+        <v>132</v>
+      </c>
+      <c r="AE10" s="13"/>
+      <c r="AI10" s="13"/>
+      <c r="AJ10" s="13"/>
+    </row>
+    <row r="11" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="10">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C11" s="10">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="D11" s="10">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="E11" s="13"/>
+      <c r="F11" s="10">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="G11" s="10">
+        <f t="shared" si="4"/>
+        <v>30</v>
+      </c>
+      <c r="H11" s="10">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="I11" s="13"/>
+      <c r="J11" s="10">
+        <f t="shared" si="6"/>
+        <v>30</v>
+      </c>
+      <c r="K11" s="10">
+        <f t="shared" si="7"/>
+        <v>17</v>
+      </c>
+      <c r="L11" s="10">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M11" s="13"/>
+      <c r="N11" s="10">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O11" s="10">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P11" s="10">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="S11" s="13"/>
+      <c r="T11" s="10">
+        <v>230</v>
+      </c>
+      <c r="U11" s="10">
+        <v>255</v>
+      </c>
+      <c r="V11" s="10">
+        <v>132</v>
+      </c>
+      <c r="W11" s="13"/>
+      <c r="X11" s="10">
+        <v>247</v>
+      </c>
+      <c r="Y11" s="10">
+        <v>247</v>
+      </c>
+      <c r="Z11" s="10">
+        <v>32</v>
+      </c>
+      <c r="AA11" s="13"/>
+      <c r="AB11" s="10">
+        <v>247</v>
+      </c>
+      <c r="AC11" s="10">
+        <v>140</v>
+      </c>
+      <c r="AD11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="13"/>
+      <c r="AI11" s="13"/>
+      <c r="AJ11" s="13"/>
+    </row>
+    <row r="12" spans="1:36" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="11">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C12" s="11">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="D12" s="11">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="E12" s="13"/>
+      <c r="F12" s="11">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="G12" s="11">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="H12" s="11">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="I12" s="13"/>
+      <c r="J12" s="11">
+        <f t="shared" si="6"/>
+        <v>11</v>
+      </c>
+      <c r="K12" s="11">
+        <f t="shared" si="7"/>
+        <v>14</v>
+      </c>
+      <c r="L12" s="11">
+        <f t="shared" si="8"/>
+        <v>15</v>
+      </c>
+      <c r="M12" s="13"/>
+      <c r="N12" s="11">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O12" s="11">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P12" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="13"/>
+      <c r="R12" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="S12" s="13"/>
+      <c r="T12" s="11">
+        <v>230</v>
+      </c>
+      <c r="U12" s="11">
+        <v>255</v>
+      </c>
+      <c r="V12" s="11">
+        <v>132</v>
+      </c>
+      <c r="W12" s="13"/>
+      <c r="X12" s="11">
+        <v>255</v>
+      </c>
+      <c r="Y12" s="11">
+        <v>178</v>
+      </c>
+      <c r="Z12" s="11">
+        <v>82</v>
+      </c>
+      <c r="AA12" s="13"/>
+      <c r="AB12" s="11">
+        <v>90</v>
+      </c>
+      <c r="AC12" s="11">
+        <v>115</v>
+      </c>
+      <c r="AD12" s="11">
+        <v>123</v>
+      </c>
+      <c r="AE12" s="13"/>
+      <c r="AI12" s="13"/>
+      <c r="AJ12" s="13"/>
+    </row>
+    <row r="13" spans="1:36" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="15">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C13" s="15">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="D13" s="15">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="E13" s="13"/>
+      <c r="F13" s="15">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="G13" s="15">
+        <f t="shared" si="4"/>
+        <v>23</v>
+      </c>
+      <c r="H13" s="15">
+        <f t="shared" si="5"/>
+        <v>23</v>
+      </c>
+      <c r="I13" s="13"/>
+      <c r="J13" s="15">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="K13" s="15">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="L13" s="15">
+        <f t="shared" si="8"/>
+        <v>7</v>
+      </c>
+      <c r="M13" s="13"/>
+      <c r="N13" s="15">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O13" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P13" s="15">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="13"/>
+      <c r="R13" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="S13" s="13"/>
+      <c r="T13" s="15">
+        <v>230</v>
+      </c>
+      <c r="U13" s="15">
+        <v>255</v>
+      </c>
+      <c r="V13" s="15">
+        <v>132</v>
+      </c>
+      <c r="W13" s="13"/>
+      <c r="X13" s="15">
+        <v>191</v>
+      </c>
+      <c r="Y13" s="15">
+        <v>191</v>
+      </c>
+      <c r="Z13" s="15">
+        <v>191</v>
+      </c>
+      <c r="AA13" s="13"/>
+      <c r="AB13" s="15">
+        <v>58</v>
+      </c>
+      <c r="AC13" s="15">
+        <v>58</v>
+      </c>
+      <c r="AD13" s="15">
+        <v>58</v>
+      </c>
+      <c r="AE13" s="13"/>
+      <c r="AI13" s="13"/>
+      <c r="AJ13" s="13"/>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="U46" s="3">
-        <f>ROUND(U42/8.2258064516129, 0)</f>
+    </row>
+    <row r="16" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="4">
+        <f t="shared" ref="B16:B27" si="12">ROUND(T16/8.2258064516129, 0)</f>
+        <v>27</v>
+      </c>
+      <c r="C16" s="4">
+        <f t="shared" ref="C16:C27" si="13">ROUND(U16/8.2258064516129, 0)</f>
+        <v>31</v>
+      </c>
+      <c r="D16" s="4">
+        <f t="shared" ref="D16:D27" si="14">ROUND(V16/8.2258064516129, 0)</f>
+        <v>27</v>
+      </c>
+      <c r="E16" s="13"/>
+      <c r="F16" s="4">
+        <f t="shared" ref="F16:F27" si="15">ROUND(X16/8.2258064516129, 0)</f>
+        <v>31</v>
+      </c>
+      <c r="G16" s="4">
+        <f t="shared" ref="G16:G27" si="16">ROUND(Y16/8.2258064516129, 0)</f>
+        <v>22</v>
+      </c>
+      <c r="H16" s="4">
+        <f t="shared" ref="H16:H27" si="17">ROUND(Z16/8.2258064516129, 0)</f>
+        <v>10</v>
+      </c>
+      <c r="I16" s="13"/>
+      <c r="J16" s="4">
+        <f t="shared" ref="J16:J27" si="18">ROUND(AB16/8.2258064516129, 0)</f>
+        <v>31</v>
+      </c>
+      <c r="K16" s="4">
+        <f t="shared" ref="K16:K27" si="19">ROUND(AC16/8.2258064516129, 0)</f>
+        <v>7</v>
+      </c>
+      <c r="L16" s="4">
+        <f t="shared" ref="L16:L27" si="20">ROUND(AD16/8.2258064516129, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="M16" s="13"/>
+      <c r="N16" s="4">
+        <f t="shared" ref="N16:N27" si="21">ROUND(AF16/8.2258064516129, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="4">
+        <f t="shared" ref="O16:O27" si="22">ROUND(AG16/8.2258064516129, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="4">
+        <f t="shared" ref="P16:P27" si="23">ROUND(AH16/8.2258064516129, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="13"/>
+      <c r="R16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="S16" s="13"/>
+      <c r="T16" s="4">
+        <v>222</v>
+      </c>
+      <c r="U16" s="4">
+        <v>255</v>
+      </c>
+      <c r="V16" s="4">
+        <v>222</v>
+      </c>
+      <c r="W16" s="13"/>
+      <c r="X16" s="4">
+        <v>255</v>
+      </c>
+      <c r="Y16" s="4">
+        <v>178</v>
+      </c>
+      <c r="Z16" s="4">
+        <v>82</v>
+      </c>
+      <c r="AA16" s="13"/>
+      <c r="AB16" s="4">
+        <v>255</v>
+      </c>
+      <c r="AC16" s="4">
+        <v>58</v>
+      </c>
+      <c r="AD16" s="4">
+        <v>8</v>
+      </c>
+      <c r="AE16" s="13"/>
+      <c r="AI16" s="13"/>
+      <c r="AJ16" s="13"/>
+    </row>
+    <row r="17" spans="1:36" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="14">
+        <f t="shared" si="12"/>
+        <v>27</v>
+      </c>
+      <c r="C17" s="14">
+        <f t="shared" si="13"/>
+        <v>31</v>
+      </c>
+      <c r="D17" s="14">
+        <f t="shared" si="14"/>
+        <v>27</v>
+      </c>
+      <c r="E17" s="13"/>
+      <c r="F17" s="14">
+        <f t="shared" si="15"/>
+        <v>31</v>
+      </c>
+      <c r="G17" s="14">
+        <f t="shared" si="16"/>
+        <v>22</v>
+      </c>
+      <c r="H17" s="14">
+        <f t="shared" si="17"/>
+        <v>10</v>
+      </c>
+      <c r="I17" s="13"/>
+      <c r="J17" s="14">
+        <f t="shared" si="18"/>
+        <v>10</v>
+      </c>
+      <c r="K17" s="14">
+        <f t="shared" si="19"/>
+        <v>9</v>
+      </c>
+      <c r="L17" s="14">
+        <f t="shared" si="20"/>
+        <v>31</v>
+      </c>
+      <c r="M17" s="13"/>
+      <c r="N17" s="14">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="O17" s="14">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="P17" s="14">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="S17" s="13"/>
+      <c r="T17" s="14">
+        <v>222</v>
+      </c>
+      <c r="U17" s="14">
+        <v>255</v>
+      </c>
+      <c r="V17" s="14">
+        <v>222</v>
+      </c>
+      <c r="W17" s="13"/>
+      <c r="X17" s="14">
+        <v>255</v>
+      </c>
+      <c r="Y17" s="14">
+        <v>178</v>
+      </c>
+      <c r="Z17" s="14">
+        <v>82</v>
+      </c>
+      <c r="AA17" s="13"/>
+      <c r="AB17" s="14">
+        <v>82</v>
+      </c>
+      <c r="AC17" s="14">
+        <v>74</v>
+      </c>
+      <c r="AD17" s="14">
+        <v>255</v>
+      </c>
+      <c r="AE17" s="13"/>
+      <c r="AI17" s="13"/>
+      <c r="AJ17" s="13"/>
+    </row>
+    <row r="18" spans="1:36" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="5">
+        <f t="shared" si="12"/>
+        <v>27</v>
+      </c>
+      <c r="C18" s="5">
+        <f t="shared" si="13"/>
+        <v>31</v>
+      </c>
+      <c r="D18" s="5">
+        <f t="shared" si="14"/>
+        <v>27</v>
+      </c>
+      <c r="E18" s="13"/>
+      <c r="F18" s="5">
+        <f t="shared" si="15"/>
+        <v>31</v>
+      </c>
+      <c r="G18" s="5">
+        <f t="shared" si="16"/>
+        <v>22</v>
+      </c>
+      <c r="H18" s="5">
+        <f t="shared" si="17"/>
+        <v>10</v>
+      </c>
+      <c r="I18" s="13"/>
+      <c r="J18" s="5">
+        <f t="shared" si="18"/>
+        <v>7</v>
+      </c>
+      <c r="K18" s="5">
+        <f t="shared" si="19"/>
+        <v>23</v>
+      </c>
+      <c r="L18" s="5">
+        <f t="shared" si="20"/>
         <v>3</v>
       </c>
-      <c r="V46" s="3">
-        <f>ROUND(V42/8.2258064516129, 0)</f>
+      <c r="M18" s="13"/>
+      <c r="N18" s="5">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="O18" s="5">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="P18" s="5">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="S18" s="13"/>
+      <c r="T18" s="5">
+        <v>222</v>
+      </c>
+      <c r="U18" s="5">
+        <v>255</v>
+      </c>
+      <c r="V18" s="5">
+        <v>222</v>
+      </c>
+      <c r="W18" s="13"/>
+      <c r="X18" s="5">
+        <v>255</v>
+      </c>
+      <c r="Y18" s="5">
+        <v>178</v>
+      </c>
+      <c r="Z18" s="5">
+        <v>82</v>
+      </c>
+      <c r="AA18" s="13"/>
+      <c r="AB18" s="5">
+        <v>58</v>
+      </c>
+      <c r="AC18" s="5">
+        <v>189</v>
+      </c>
+      <c r="AD18" s="5">
+        <v>25</v>
+      </c>
+      <c r="AE18" s="13"/>
+      <c r="AI18" s="13"/>
+      <c r="AJ18" s="13"/>
+    </row>
+    <row r="19" spans="1:36" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="W46" s="3"/>
-      <c r="X46" s="3">
-        <f>ROUND(X42/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="Y46" s="3">
-        <f>ROUND(Y42/8.2258064516129, 0)</f>
+      <c r="B19" s="7">
+        <f t="shared" si="12"/>
+        <v>27</v>
+      </c>
+      <c r="C19" s="7">
+        <f t="shared" si="13"/>
+        <v>31</v>
+      </c>
+      <c r="D19" s="7">
+        <f t="shared" si="14"/>
+        <v>27</v>
+      </c>
+      <c r="E19" s="13"/>
+      <c r="F19" s="7">
+        <f t="shared" si="15"/>
+        <v>31</v>
+      </c>
+      <c r="G19" s="7">
+        <f t="shared" si="16"/>
+        <v>22</v>
+      </c>
+      <c r="H19" s="7">
+        <f t="shared" si="17"/>
+        <v>10</v>
+      </c>
+      <c r="I19" s="13"/>
+      <c r="J19" s="7">
+        <f t="shared" si="18"/>
+        <v>15</v>
+      </c>
+      <c r="K19" s="7">
+        <f t="shared" si="19"/>
+        <v>10</v>
+      </c>
+      <c r="L19" s="7">
+        <f t="shared" si="20"/>
+        <v>3</v>
+      </c>
+      <c r="M19" s="13"/>
+      <c r="N19" s="7">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="O19" s="7">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="P19" s="7">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="13"/>
+      <c r="R19" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="S19" s="13"/>
+      <c r="T19" s="7">
+        <v>222</v>
+      </c>
+      <c r="U19" s="7">
+        <v>255</v>
+      </c>
+      <c r="V19" s="7">
+        <v>222</v>
+      </c>
+      <c r="W19" s="13"/>
+      <c r="X19" s="7">
+        <v>255</v>
+      </c>
+      <c r="Y19" s="7">
+        <v>178</v>
+      </c>
+      <c r="Z19" s="7">
+        <v>82</v>
+      </c>
+      <c r="AA19" s="13"/>
+      <c r="AB19" s="7">
+        <v>123</v>
+      </c>
+      <c r="AC19" s="7">
+        <v>82</v>
+      </c>
+      <c r="AD19" s="7">
+        <v>25</v>
+      </c>
+      <c r="AE19" s="13"/>
+      <c r="AI19" s="13"/>
+      <c r="AJ19" s="13"/>
+    </row>
+    <row r="20" spans="1:36" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="16">
+        <f t="shared" si="12"/>
+        <v>27</v>
+      </c>
+      <c r="C20" s="16">
+        <f t="shared" si="13"/>
+        <v>31</v>
+      </c>
+      <c r="D20" s="16">
+        <f t="shared" si="14"/>
+        <v>27</v>
+      </c>
+      <c r="E20" s="13"/>
+      <c r="F20" s="16">
+        <f t="shared" si="15"/>
+        <v>31</v>
+      </c>
+      <c r="G20" s="16">
+        <f t="shared" si="16"/>
+        <v>22</v>
+      </c>
+      <c r="H20" s="16">
+        <f t="shared" si="17"/>
+        <v>10</v>
+      </c>
+      <c r="I20" s="13"/>
+      <c r="J20" s="16">
+        <f t="shared" si="18"/>
+        <v>20</v>
+      </c>
+      <c r="K20" s="16">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="L20" s="16">
+        <f t="shared" si="20"/>
+        <v>20</v>
+      </c>
+      <c r="M20" s="13"/>
+      <c r="N20" s="16">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="O20" s="16">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="P20" s="16">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="13"/>
+      <c r="R20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="S20" s="13"/>
+      <c r="T20" s="16">
+        <v>222</v>
+      </c>
+      <c r="U20" s="16">
+        <v>255</v>
+      </c>
+      <c r="V20" s="16">
+        <v>222</v>
+      </c>
+      <c r="W20" s="13"/>
+      <c r="X20" s="16">
+        <v>255</v>
+      </c>
+      <c r="Y20" s="16">
+        <v>178</v>
+      </c>
+      <c r="Z20" s="16">
+        <v>82</v>
+      </c>
+      <c r="AA20" s="13"/>
+      <c r="AB20" s="16">
+        <v>165</v>
+      </c>
+      <c r="AC20" s="16">
+        <v>8</v>
+      </c>
+      <c r="AD20" s="16">
+        <v>165</v>
+      </c>
+      <c r="AE20" s="13"/>
+      <c r="AI20" s="13"/>
+      <c r="AJ20" s="13"/>
+    </row>
+    <row r="21" spans="1:36" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="6">
+        <f t="shared" si="12"/>
+        <v>27</v>
+      </c>
+      <c r="C21" s="6">
+        <f t="shared" si="13"/>
+        <v>31</v>
+      </c>
+      <c r="D21" s="6">
+        <f t="shared" si="14"/>
+        <v>27</v>
+      </c>
+      <c r="E21" s="13"/>
+      <c r="F21" s="6">
+        <f t="shared" si="15"/>
+        <v>31</v>
+      </c>
+      <c r="G21" s="6">
+        <f t="shared" si="16"/>
+        <v>22</v>
+      </c>
+      <c r="H21" s="6">
+        <f t="shared" si="17"/>
+        <v>10</v>
+      </c>
+      <c r="I21" s="13"/>
+      <c r="J21" s="6">
+        <f t="shared" si="18"/>
+        <v>23</v>
+      </c>
+      <c r="K21" s="6">
+        <f t="shared" si="19"/>
+        <v>23</v>
+      </c>
+      <c r="L21" s="6">
+        <f t="shared" si="20"/>
+        <v>23</v>
+      </c>
+      <c r="M21" s="13"/>
+      <c r="N21" s="6">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="O21" s="6">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="P21" s="6">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="Q21" s="13"/>
+      <c r="R21" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="S21" s="13"/>
+      <c r="T21" s="6">
+        <v>222</v>
+      </c>
+      <c r="U21" s="6">
+        <v>255</v>
+      </c>
+      <c r="V21" s="6">
+        <v>222</v>
+      </c>
+      <c r="W21" s="13"/>
+      <c r="X21" s="6">
+        <v>255</v>
+      </c>
+      <c r="Y21" s="6">
+        <v>178</v>
+      </c>
+      <c r="Z21" s="6">
+        <v>82</v>
+      </c>
+      <c r="AA21" s="13"/>
+      <c r="AB21" s="6">
+        <v>191</v>
+      </c>
+      <c r="AC21" s="6">
+        <v>191</v>
+      </c>
+      <c r="AD21" s="6">
+        <v>191</v>
+      </c>
+      <c r="AE21" s="13"/>
+      <c r="AI21" s="13"/>
+      <c r="AJ21" s="13"/>
+    </row>
+    <row r="22" spans="1:36" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="8">
+        <f t="shared" si="12"/>
+        <v>27</v>
+      </c>
+      <c r="C22" s="8">
+        <f t="shared" si="13"/>
+        <v>31</v>
+      </c>
+      <c r="D22" s="8">
+        <f t="shared" si="14"/>
+        <v>27</v>
+      </c>
+      <c r="E22" s="13"/>
+      <c r="F22" s="8">
+        <f t="shared" si="15"/>
+        <v>12</v>
+      </c>
+      <c r="G22" s="8">
+        <f t="shared" si="16"/>
+        <v>25</v>
+      </c>
+      <c r="H22" s="8">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+      <c r="I22" s="13"/>
+      <c r="J22" s="8">
+        <f t="shared" si="18"/>
+        <v>5</v>
+      </c>
+      <c r="K22" s="8">
+        <f t="shared" si="19"/>
+        <v>14</v>
+      </c>
+      <c r="L22" s="8">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="M22" s="13"/>
+      <c r="N22" s="8">
+        <f t="shared" si="21"/>
+        <v>7</v>
+      </c>
+      <c r="O22" s="8">
+        <f t="shared" si="22"/>
+        <v>7</v>
+      </c>
+      <c r="P22" s="8">
+        <f t="shared" si="23"/>
+        <v>7</v>
+      </c>
+      <c r="Q22" s="13"/>
+      <c r="R22" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="S22" s="13"/>
+      <c r="T22" s="8">
+        <v>222</v>
+      </c>
+      <c r="U22" s="8">
+        <v>255</v>
+      </c>
+      <c r="V22" s="8">
+        <v>222</v>
+      </c>
+      <c r="W22" s="13"/>
+      <c r="X22" s="8">
+        <v>99</v>
+      </c>
+      <c r="Y22" s="8">
+        <v>206</v>
+      </c>
+      <c r="Z22" s="8">
+        <v>8</v>
+      </c>
+      <c r="AA22" s="13"/>
+      <c r="AB22" s="8">
+        <v>41</v>
+      </c>
+      <c r="AC22" s="8">
+        <v>115</v>
+      </c>
+      <c r="AD22" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="13"/>
+      <c r="AF22" s="8">
+        <v>58</v>
+      </c>
+      <c r="AG22" s="8">
+        <v>58</v>
+      </c>
+      <c r="AH22" s="8">
+        <v>58</v>
+      </c>
+      <c r="AI22" s="13"/>
+      <c r="AJ22" s="13"/>
+    </row>
+    <row r="23" spans="1:36" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="7">
+        <f t="shared" si="12"/>
+        <v>27</v>
+      </c>
+      <c r="C23" s="7">
+        <f t="shared" si="13"/>
+        <v>31</v>
+      </c>
+      <c r="D23" s="7">
+        <f t="shared" si="14"/>
+        <v>27</v>
+      </c>
+      <c r="E23" s="13"/>
+      <c r="F23" s="7">
+        <f t="shared" si="15"/>
         <v>24</v>
       </c>
-      <c r="Z46" s="3">
-        <f>ROUND(Z42/8.2258064516129, 0)</f>
+      <c r="G23" s="7">
+        <f t="shared" si="16"/>
+        <v>18</v>
+      </c>
+      <c r="H23" s="7">
+        <f t="shared" si="17"/>
+        <v>7</v>
+      </c>
+      <c r="I23" s="13"/>
+      <c r="J23" s="7">
+        <f t="shared" si="18"/>
+        <v>15</v>
+      </c>
+      <c r="K23" s="7">
+        <f t="shared" si="19"/>
+        <v>10</v>
+      </c>
+      <c r="L23" s="7">
+        <f t="shared" si="20"/>
+        <v>3</v>
+      </c>
+      <c r="M23" s="13"/>
+      <c r="N23" s="7">
+        <f t="shared" si="21"/>
+        <v>7</v>
+      </c>
+      <c r="O23" s="7">
+        <f t="shared" si="22"/>
+        <v>7</v>
+      </c>
+      <c r="P23" s="7">
+        <f t="shared" si="23"/>
+        <v>7</v>
+      </c>
+      <c r="Q23" s="13"/>
+      <c r="R23" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="S23" s="13"/>
+      <c r="T23" s="7">
+        <v>222</v>
+      </c>
+      <c r="U23" s="7">
+        <v>255</v>
+      </c>
+      <c r="V23" s="7">
+        <v>222</v>
+      </c>
+      <c r="W23" s="13"/>
+      <c r="X23" s="7">
+        <v>197</v>
+      </c>
+      <c r="Y23" s="7">
+        <v>148</v>
+      </c>
+      <c r="Z23" s="7">
+        <v>58</v>
+      </c>
+      <c r="AA23" s="13"/>
+      <c r="AB23" s="7">
+        <v>123</v>
+      </c>
+      <c r="AC23" s="7">
+        <v>82</v>
+      </c>
+      <c r="AD23" s="7">
+        <v>25</v>
+      </c>
+      <c r="AE23" s="13"/>
+      <c r="AF23" s="7">
+        <v>58</v>
+      </c>
+      <c r="AG23" s="7">
+        <v>58</v>
+      </c>
+      <c r="AH23" s="7">
+        <v>58</v>
+      </c>
+      <c r="AI23" s="13"/>
+      <c r="AJ23" s="13"/>
+    </row>
+    <row r="24" spans="1:36" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="9">
+        <f t="shared" si="12"/>
+        <v>27</v>
+      </c>
+      <c r="C24" s="9">
+        <f t="shared" si="13"/>
+        <v>31</v>
+      </c>
+      <c r="D24" s="9">
+        <f t="shared" si="14"/>
+        <v>27</v>
+      </c>
+      <c r="E24" s="13"/>
+      <c r="F24" s="9">
+        <f t="shared" si="15"/>
+        <v>31</v>
+      </c>
+      <c r="G24" s="9">
+        <f t="shared" si="16"/>
+        <v>22</v>
+      </c>
+      <c r="H24" s="9">
+        <f t="shared" si="17"/>
+        <v>10</v>
+      </c>
+      <c r="I24" s="13"/>
+      <c r="J24" s="9">
+        <f t="shared" si="18"/>
+        <v>27</v>
+      </c>
+      <c r="K24" s="9">
+        <f t="shared" si="19"/>
+        <v>7</v>
+      </c>
+      <c r="L24" s="9">
+        <f t="shared" si="20"/>
+        <v>16</v>
+      </c>
+      <c r="M24" s="13"/>
+      <c r="N24" s="9">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="O24" s="9">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="P24" s="9">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="13"/>
+      <c r="R24" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="S24" s="13"/>
+      <c r="T24" s="9">
+        <v>222</v>
+      </c>
+      <c r="U24" s="9">
+        <v>255</v>
+      </c>
+      <c r="V24" s="9">
+        <v>222</v>
+      </c>
+      <c r="W24" s="13"/>
+      <c r="X24" s="9">
+        <v>255</v>
+      </c>
+      <c r="Y24" s="9">
+        <v>178</v>
+      </c>
+      <c r="Z24" s="9">
+        <v>82</v>
+      </c>
+      <c r="AA24" s="13"/>
+      <c r="AB24" s="9">
+        <v>222</v>
+      </c>
+      <c r="AC24" s="9">
+        <v>58</v>
+      </c>
+      <c r="AD24" s="9">
+        <v>132</v>
+      </c>
+      <c r="AE24" s="13"/>
+      <c r="AI24" s="13"/>
+      <c r="AJ24" s="13"/>
+    </row>
+    <row r="25" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="10">
+        <f t="shared" si="12"/>
+        <v>27</v>
+      </c>
+      <c r="C25" s="10">
+        <f t="shared" si="13"/>
+        <v>31</v>
+      </c>
+      <c r="D25" s="10">
+        <f t="shared" si="14"/>
+        <v>27</v>
+      </c>
+      <c r="E25" s="13"/>
+      <c r="F25" s="10">
+        <f t="shared" si="15"/>
+        <v>30</v>
+      </c>
+      <c r="G25" s="10">
+        <f t="shared" si="16"/>
+        <v>30</v>
+      </c>
+      <c r="H25" s="10">
+        <f t="shared" si="17"/>
+        <v>4</v>
+      </c>
+      <c r="I25" s="13"/>
+      <c r="J25" s="10">
+        <f t="shared" si="18"/>
+        <v>30</v>
+      </c>
+      <c r="K25" s="10">
+        <f t="shared" si="19"/>
+        <v>17</v>
+      </c>
+      <c r="L25" s="10">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="M25" s="13"/>
+      <c r="N25" s="10">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="O25" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="P25" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="Q25" s="13"/>
+      <c r="R25" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="S25" s="13"/>
+      <c r="T25" s="10">
+        <v>222</v>
+      </c>
+      <c r="U25" s="10">
+        <v>255</v>
+      </c>
+      <c r="V25" s="10">
+        <v>222</v>
+      </c>
+      <c r="W25" s="13"/>
+      <c r="X25" s="10">
+        <v>247</v>
+      </c>
+      <c r="Y25" s="10">
+        <v>247</v>
+      </c>
+      <c r="Z25" s="10">
+        <v>32</v>
+      </c>
+      <c r="AA25" s="13"/>
+      <c r="AB25" s="10">
+        <v>247</v>
+      </c>
+      <c r="AC25" s="10">
+        <v>140</v>
+      </c>
+      <c r="AD25" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="13"/>
+      <c r="AI25" s="13"/>
+      <c r="AJ25" s="13"/>
+    </row>
+    <row r="26" spans="1:36" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="11">
+        <f t="shared" si="12"/>
+        <v>27</v>
+      </c>
+      <c r="C26" s="11">
+        <f t="shared" si="13"/>
+        <v>31</v>
+      </c>
+      <c r="D26" s="11">
+        <f t="shared" si="14"/>
+        <v>27</v>
+      </c>
+      <c r="E26" s="13"/>
+      <c r="F26" s="11">
+        <f t="shared" si="15"/>
+        <v>31</v>
+      </c>
+      <c r="G26" s="11">
+        <f t="shared" si="16"/>
+        <v>22</v>
+      </c>
+      <c r="H26" s="11">
+        <f t="shared" si="17"/>
+        <v>10</v>
+      </c>
+      <c r="I26" s="13"/>
+      <c r="J26" s="11">
+        <f t="shared" si="18"/>
+        <v>11</v>
+      </c>
+      <c r="K26" s="11">
+        <f t="shared" si="19"/>
+        <v>14</v>
+      </c>
+      <c r="L26" s="11">
+        <f t="shared" si="20"/>
+        <v>15</v>
+      </c>
+      <c r="M26" s="13"/>
+      <c r="N26" s="11">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="O26" s="11">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="P26" s="11">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="13"/>
+      <c r="R26" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="S26" s="13"/>
+      <c r="T26" s="11">
+        <v>222</v>
+      </c>
+      <c r="U26" s="11">
+        <v>255</v>
+      </c>
+      <c r="V26" s="11">
+        <v>222</v>
+      </c>
+      <c r="W26" s="13"/>
+      <c r="X26" s="11">
+        <v>255</v>
+      </c>
+      <c r="Y26" s="11">
+        <v>178</v>
+      </c>
+      <c r="Z26" s="11">
+        <v>82</v>
+      </c>
+      <c r="AA26" s="13"/>
+      <c r="AB26" s="11">
+        <v>90</v>
+      </c>
+      <c r="AC26" s="11">
+        <v>115</v>
+      </c>
+      <c r="AD26" s="11">
+        <v>123</v>
+      </c>
+      <c r="AE26" s="13"/>
+      <c r="AI26" s="13"/>
+      <c r="AJ26" s="13"/>
+    </row>
+    <row r="27" spans="1:36" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="15">
+        <f t="shared" si="12"/>
+        <v>27</v>
+      </c>
+      <c r="C27" s="15">
+        <f t="shared" si="13"/>
+        <v>31</v>
+      </c>
+      <c r="D27" s="15">
+        <f t="shared" si="14"/>
+        <v>27</v>
+      </c>
+      <c r="E27" s="13"/>
+      <c r="F27" s="15">
+        <f t="shared" si="15"/>
+        <v>23</v>
+      </c>
+      <c r="G27" s="15">
+        <f t="shared" si="16"/>
+        <v>23</v>
+      </c>
+      <c r="H27" s="15">
+        <f t="shared" si="17"/>
+        <v>23</v>
+      </c>
+      <c r="I27" s="13"/>
+      <c r="J27" s="15">
+        <f t="shared" si="18"/>
+        <v>7</v>
+      </c>
+      <c r="K27" s="15">
+        <f t="shared" si="19"/>
+        <v>7</v>
+      </c>
+      <c r="L27" s="15">
+        <f t="shared" si="20"/>
+        <v>7</v>
+      </c>
+      <c r="M27" s="13"/>
+      <c r="N27" s="15">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="O27" s="15">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="P27" s="15">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="13"/>
+      <c r="R27" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="S27" s="13"/>
+      <c r="T27" s="15">
+        <v>222</v>
+      </c>
+      <c r="U27" s="15">
+        <v>255</v>
+      </c>
+      <c r="V27" s="15">
+        <v>222</v>
+      </c>
+      <c r="W27" s="13"/>
+      <c r="X27" s="15">
+        <v>191</v>
+      </c>
+      <c r="Y27" s="15">
+        <v>191</v>
+      </c>
+      <c r="Z27" s="15">
+        <v>191</v>
+      </c>
+      <c r="AA27" s="13"/>
+      <c r="AB27" s="15">
+        <v>58</v>
+      </c>
+      <c r="AC27" s="15">
+        <v>58</v>
+      </c>
+      <c r="AD27" s="15">
+        <v>58</v>
+      </c>
+      <c r="AE27" s="13"/>
+      <c r="AI27" s="13"/>
+      <c r="AJ27" s="13"/>
+    </row>
+    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="4">
+        <f t="shared" ref="B30:B41" si="24">ROUND(T30/8.2258064516129, 0)</f>
+        <v>15</v>
+      </c>
+      <c r="C30" s="4">
+        <f t="shared" ref="C30:C41" si="25">ROUND(U30/8.2258064516129, 0)</f>
+        <v>14</v>
+      </c>
+      <c r="D30" s="4">
+        <f t="shared" ref="D30:D41" si="26">ROUND(V30/8.2258064516129, 0)</f>
+        <v>24</v>
+      </c>
+      <c r="E30" s="13"/>
+      <c r="F30" s="4">
+        <f t="shared" ref="F30:F41" si="27">ROUND(X30/8.2258064516129, 0)</f>
+        <v>26</v>
+      </c>
+      <c r="G30" s="4">
+        <f t="shared" ref="G30:G41" si="28">ROUND(Y30/8.2258064516129, 0)</f>
+        <v>18</v>
+      </c>
+      <c r="H30" s="4">
+        <f t="shared" ref="H30:H41" si="29">ROUND(Z30/8.2258064516129, 0)</f>
+        <v>9</v>
+      </c>
+      <c r="I30" s="13"/>
+      <c r="J30" s="4">
+        <f t="shared" ref="J30:J41" si="30">ROUND(AB30/8.2258064516129, 0)</f>
+        <v>25</v>
+      </c>
+      <c r="K30" s="4">
+        <f t="shared" ref="K30:K41" si="31">ROUND(AC30/8.2258064516129, 0)</f>
+        <v>6</v>
+      </c>
+      <c r="L30" s="4">
+        <f t="shared" ref="L30:L41" si="32">ROUND(AD30/8.2258064516129, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="M30" s="13"/>
+      <c r="N30" s="4">
+        <f t="shared" ref="N30:N41" si="33">ROUND(AF30/8.2258064516129, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="O30" s="4">
+        <f t="shared" ref="O30:O41" si="34">ROUND(AG30/8.2258064516129, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="P30" s="4">
+        <f t="shared" ref="P30:P41" si="35">ROUND(AH30/8.2258064516129, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="13"/>
+      <c r="R30" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="S30" s="13"/>
+      <c r="T30" s="4">
+        <v>123</v>
+      </c>
+      <c r="U30" s="4">
+        <v>115</v>
+      </c>
+      <c r="V30" s="4">
+        <v>197</v>
+      </c>
+      <c r="W30" s="13"/>
+      <c r="X30" s="4">
+        <v>217</v>
+      </c>
+      <c r="Y30" s="4">
+        <v>151</v>
+      </c>
+      <c r="Z30" s="4">
+        <v>70</v>
+      </c>
+      <c r="AA30" s="13"/>
+      <c r="AB30" s="4">
+        <v>204</v>
+      </c>
+      <c r="AC30" s="4">
+        <v>46</v>
+      </c>
+      <c r="AD30" s="4">
+        <v>6</v>
+      </c>
+      <c r="AE30" s="13"/>
+      <c r="AI30" s="13"/>
+      <c r="AJ30" s="13"/>
+    </row>
+    <row r="31" spans="1:36" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="14">
+        <f t="shared" si="24"/>
+        <v>15</v>
+      </c>
+      <c r="C31" s="14">
+        <f t="shared" si="25"/>
+        <v>14</v>
+      </c>
+      <c r="D31" s="14">
+        <f t="shared" si="26"/>
+        <v>24</v>
+      </c>
+      <c r="E31" s="13"/>
+      <c r="F31" s="14">
+        <f t="shared" si="27"/>
+        <v>26</v>
+      </c>
+      <c r="G31" s="14">
+        <f t="shared" si="28"/>
+        <v>18</v>
+      </c>
+      <c r="H31" s="14">
+        <f t="shared" si="29"/>
+        <v>9</v>
+      </c>
+      <c r="I31" s="13"/>
+      <c r="J31" s="14">
+        <f t="shared" si="30"/>
+        <v>8</v>
+      </c>
+      <c r="K31" s="14">
+        <f t="shared" si="31"/>
+        <v>7</v>
+      </c>
+      <c r="L31" s="14">
+        <f t="shared" si="32"/>
+        <v>25</v>
+      </c>
+      <c r="M31" s="13"/>
+      <c r="N31" s="14">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="O31" s="14">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="P31" s="14">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="13"/>
+      <c r="R31" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="S31" s="13"/>
+      <c r="T31" s="14">
+        <v>123</v>
+      </c>
+      <c r="U31" s="14">
+        <v>115</v>
+      </c>
+      <c r="V31" s="14">
+        <v>197</v>
+      </c>
+      <c r="W31" s="13"/>
+      <c r="X31" s="14">
+        <v>217</v>
+      </c>
+      <c r="Y31" s="14">
+        <v>151</v>
+      </c>
+      <c r="Z31" s="14">
+        <v>70</v>
+      </c>
+      <c r="AA31" s="13"/>
+      <c r="AB31" s="14">
+        <v>66</v>
+      </c>
+      <c r="AC31" s="14">
+        <v>59</v>
+      </c>
+      <c r="AD31" s="14">
+        <v>204</v>
+      </c>
+      <c r="AE31" s="13"/>
+      <c r="AI31" s="13"/>
+      <c r="AJ31" s="13"/>
+    </row>
+    <row r="32" spans="1:36" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="5">
+        <f t="shared" si="24"/>
+        <v>15</v>
+      </c>
+      <c r="C32" s="5">
+        <f t="shared" si="25"/>
+        <v>14</v>
+      </c>
+      <c r="D32" s="5">
+        <f t="shared" si="26"/>
+        <v>24</v>
+      </c>
+      <c r="E32" s="13"/>
+      <c r="F32" s="5">
+        <f t="shared" si="27"/>
+        <v>26</v>
+      </c>
+      <c r="G32" s="5">
+        <f t="shared" si="28"/>
+        <v>18</v>
+      </c>
+      <c r="H32" s="5">
+        <f t="shared" si="29"/>
+        <v>9</v>
+      </c>
+      <c r="I32" s="13"/>
+      <c r="J32" s="5">
+        <f t="shared" si="30"/>
+        <v>5</v>
+      </c>
+      <c r="K32" s="5">
+        <f t="shared" si="31"/>
+        <v>17</v>
+      </c>
+      <c r="L32" s="5">
+        <f t="shared" si="32"/>
         <v>2</v>
       </c>
-      <c r="AA46" s="3"/>
-      <c r="AB46" s="3">
-        <f>ROUND(AB42/8.2258064516129, 0)</f>
+      <c r="M32" s="13"/>
+      <c r="N32" s="5">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="O32" s="5">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="P32" s="5">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="Q32" s="13"/>
+      <c r="R32" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="S32" s="13"/>
+      <c r="T32" s="5">
+        <v>123</v>
+      </c>
+      <c r="U32" s="5">
+        <v>115</v>
+      </c>
+      <c r="V32" s="5">
+        <v>197</v>
+      </c>
+      <c r="W32" s="13"/>
+      <c r="X32" s="5">
+        <v>217</v>
+      </c>
+      <c r="Y32" s="5">
+        <v>151</v>
+      </c>
+      <c r="Z32" s="5">
+        <v>70</v>
+      </c>
+      <c r="AA32" s="13"/>
+      <c r="AB32" s="5">
+        <v>42</v>
+      </c>
+      <c r="AC32" s="5">
+        <v>138</v>
+      </c>
+      <c r="AD32" s="5">
+        <v>19</v>
+      </c>
+      <c r="AE32" s="13"/>
+      <c r="AI32" s="13"/>
+      <c r="AJ32" s="13"/>
+    </row>
+    <row r="33" spans="1:36" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="AC46" s="3">
-        <f>ROUND(AC42/8.2258064516129, 0)</f>
+      <c r="B33" s="7">
+        <f t="shared" si="24"/>
+        <v>15</v>
+      </c>
+      <c r="C33" s="7">
+        <f t="shared" si="25"/>
+        <v>14</v>
+      </c>
+      <c r="D33" s="7">
+        <f t="shared" si="26"/>
+        <v>24</v>
+      </c>
+      <c r="E33" s="13"/>
+      <c r="F33" s="7">
+        <f t="shared" si="27"/>
+        <v>26</v>
+      </c>
+      <c r="G33" s="7">
+        <f t="shared" si="28"/>
+        <v>18</v>
+      </c>
+      <c r="H33" s="7">
+        <f t="shared" si="29"/>
+        <v>9</v>
+      </c>
+      <c r="I33" s="13"/>
+      <c r="J33" s="7">
+        <f t="shared" si="30"/>
+        <v>10</v>
+      </c>
+      <c r="K33" s="7">
+        <f t="shared" si="31"/>
+        <v>7</v>
+      </c>
+      <c r="L33" s="7">
+        <f t="shared" si="32"/>
+        <v>2</v>
+      </c>
+      <c r="M33" s="13"/>
+      <c r="N33" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="O33" s="7">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="P33" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="Q33" s="13"/>
+      <c r="R33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="S33" s="13"/>
+      <c r="T33" s="7">
+        <v>123</v>
+      </c>
+      <c r="U33" s="7">
+        <v>115</v>
+      </c>
+      <c r="V33" s="7">
+        <v>197</v>
+      </c>
+      <c r="W33" s="13"/>
+      <c r="X33" s="7">
+        <v>217</v>
+      </c>
+      <c r="Y33" s="7">
+        <v>151</v>
+      </c>
+      <c r="Z33" s="7">
+        <v>70</v>
+      </c>
+      <c r="AA33" s="13"/>
+      <c r="AB33" s="7">
+        <v>84</v>
+      </c>
+      <c r="AC33" s="7">
+        <v>57</v>
+      </c>
+      <c r="AD33" s="7">
+        <v>18</v>
+      </c>
+      <c r="AE33" s="13"/>
+      <c r="AI33" s="13"/>
+      <c r="AJ33" s="13"/>
+    </row>
+    <row r="34" spans="1:36" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" s="16">
+        <f t="shared" si="24"/>
+        <v>15</v>
+      </c>
+      <c r="C34" s="16">
+        <f t="shared" si="25"/>
+        <v>14</v>
+      </c>
+      <c r="D34" s="16">
+        <f t="shared" si="26"/>
+        <v>24</v>
+      </c>
+      <c r="E34" s="13"/>
+      <c r="F34" s="16">
+        <f t="shared" si="27"/>
+        <v>26</v>
+      </c>
+      <c r="G34" s="16">
+        <f t="shared" si="28"/>
+        <v>18</v>
+      </c>
+      <c r="H34" s="16">
+        <f t="shared" si="29"/>
+        <v>9</v>
+      </c>
+      <c r="I34" s="13"/>
+      <c r="J34" s="16">
+        <f t="shared" si="30"/>
+        <v>14</v>
+      </c>
+      <c r="K34" s="16">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="L34" s="16">
+        <f t="shared" si="32"/>
+        <v>14</v>
+      </c>
+      <c r="M34" s="13"/>
+      <c r="N34" s="16">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="O34" s="16">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="P34" s="16">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="Q34" s="13"/>
+      <c r="R34" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="S34" s="13"/>
+      <c r="T34" s="16">
+        <v>123</v>
+      </c>
+      <c r="U34" s="16">
+        <v>115</v>
+      </c>
+      <c r="V34" s="16">
+        <v>197</v>
+      </c>
+      <c r="W34" s="13"/>
+      <c r="X34" s="16">
+        <v>217</v>
+      </c>
+      <c r="Y34" s="16">
+        <v>151</v>
+      </c>
+      <c r="Z34" s="16">
+        <v>70</v>
+      </c>
+      <c r="AA34" s="13"/>
+      <c r="AB34" s="16">
+        <v>115</v>
+      </c>
+      <c r="AC34" s="16">
+        <v>6</v>
+      </c>
+      <c r="AD34" s="16">
+        <v>115</v>
+      </c>
+      <c r="AE34" s="13"/>
+      <c r="AI34" s="13"/>
+      <c r="AJ34" s="13"/>
+    </row>
+    <row r="35" spans="1:36" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" s="6">
+        <f t="shared" si="24"/>
+        <v>15</v>
+      </c>
+      <c r="C35" s="6">
+        <f t="shared" si="25"/>
+        <v>14</v>
+      </c>
+      <c r="D35" s="6">
+        <f t="shared" si="26"/>
+        <v>24</v>
+      </c>
+      <c r="E35" s="13"/>
+      <c r="F35" s="6">
+        <f t="shared" si="27"/>
+        <v>26</v>
+      </c>
+      <c r="G35" s="6">
+        <f t="shared" si="28"/>
+        <v>18</v>
+      </c>
+      <c r="H35" s="6">
+        <f t="shared" si="29"/>
+        <v>9</v>
+      </c>
+      <c r="I35" s="13"/>
+      <c r="J35" s="6">
+        <f t="shared" si="30"/>
+        <v>17</v>
+      </c>
+      <c r="K35" s="6">
+        <f t="shared" si="31"/>
+        <v>17</v>
+      </c>
+      <c r="L35" s="6">
+        <f t="shared" si="32"/>
+        <v>17</v>
+      </c>
+      <c r="M35" s="13"/>
+      <c r="N35" s="6">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="O35" s="6">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="P35" s="6">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="Q35" s="13"/>
+      <c r="R35" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="AD46" s="3">
-        <f>ROUND(AD42/8.2258064516129, 0)</f>
+      <c r="S35" s="13"/>
+      <c r="T35" s="6">
+        <v>123</v>
+      </c>
+      <c r="U35" s="6">
+        <v>115</v>
+      </c>
+      <c r="V35" s="6">
+        <v>197</v>
+      </c>
+      <c r="W35" s="13"/>
+      <c r="X35" s="6">
+        <v>217</v>
+      </c>
+      <c r="Y35" s="6">
+        <v>151</v>
+      </c>
+      <c r="Z35" s="6">
+        <v>70</v>
+      </c>
+      <c r="AA35" s="13"/>
+      <c r="AB35" s="6">
+        <v>140</v>
+      </c>
+      <c r="AC35" s="6">
+        <v>140</v>
+      </c>
+      <c r="AD35" s="6">
+        <v>140</v>
+      </c>
+      <c r="AE35" s="13"/>
+      <c r="AI35" s="13"/>
+      <c r="AJ35" s="13"/>
+    </row>
+    <row r="36" spans="1:36" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="8">
+        <f t="shared" si="24"/>
+        <v>15</v>
+      </c>
+      <c r="C36" s="8">
+        <f t="shared" si="25"/>
+        <v>14</v>
+      </c>
+      <c r="D36" s="8">
+        <f t="shared" si="26"/>
+        <v>24</v>
+      </c>
+      <c r="E36" s="13"/>
+      <c r="F36" s="8">
+        <f t="shared" si="27"/>
+        <v>8</v>
+      </c>
+      <c r="G36" s="8">
+        <f t="shared" si="28"/>
+        <v>13</v>
+      </c>
+      <c r="H36" s="8">
+        <f t="shared" si="29"/>
+        <v>19</v>
+      </c>
+      <c r="I36" s="13"/>
+      <c r="J36" s="8">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="8">
+        <f t="shared" si="31"/>
+        <v>11</v>
+      </c>
+      <c r="L36" s="8">
+        <f t="shared" si="32"/>
+        <v>13</v>
+      </c>
+      <c r="M36" s="13"/>
+      <c r="N36" s="8">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="O36" s="8">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="P36" s="8">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="Q36" s="13"/>
+      <c r="R36" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="S36" s="13"/>
+      <c r="T36" s="8">
+        <v>123</v>
+      </c>
+      <c r="U36" s="8">
+        <v>115</v>
+      </c>
+      <c r="V36" s="8">
+        <v>197</v>
+      </c>
+      <c r="W36" s="13"/>
+      <c r="X36" s="8">
+        <v>66</v>
+      </c>
+      <c r="Y36" s="8">
+        <v>107</v>
+      </c>
+      <c r="Z36" s="8">
+        <v>156</v>
+      </c>
+      <c r="AA36" s="13"/>
+      <c r="AB36" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>90</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>107</v>
+      </c>
+      <c r="AE36" s="13"/>
+      <c r="AI36" s="13"/>
+      <c r="AJ36" s="13"/>
+    </row>
+    <row r="37" spans="1:36" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" s="7">
+        <f t="shared" si="24"/>
+        <v>15</v>
+      </c>
+      <c r="C37" s="7">
+        <f t="shared" si="25"/>
+        <v>14</v>
+      </c>
+      <c r="D37" s="7">
+        <f t="shared" si="26"/>
+        <v>24</v>
+      </c>
+      <c r="E37" s="13"/>
+      <c r="F37" s="7">
+        <f t="shared" si="27"/>
+        <v>12</v>
+      </c>
+      <c r="G37" s="7">
+        <f t="shared" si="28"/>
         <v>9</v>
       </c>
-      <c r="AE46" s="3"/>
-      <c r="AF46" s="3">
-        <f>ROUND(AF42/8.2258064516129, 0)</f>
+      <c r="H37" s="7">
+        <f t="shared" si="29"/>
+        <v>9</v>
+      </c>
+      <c r="I37" s="13"/>
+      <c r="J37" s="7">
+        <f t="shared" si="30"/>
         <v>7</v>
       </c>
-      <c r="AG46" s="3">
-        <f>ROUND(AG42/8.2258064516129, 0)</f>
-        <v>7</v>
-      </c>
-      <c r="AH46" s="3">
-        <f>ROUND(AH42/8.2258064516129, 0)</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="T47" s="3">
-        <f>ROUND(T43/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="U47" s="3">
-        <f>ROUND(U43/8.2258064516129, 0)</f>
+      <c r="K37" s="7">
+        <f t="shared" si="31"/>
+        <v>5</v>
+      </c>
+      <c r="L37" s="7">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="M37" s="13"/>
+      <c r="N37" s="7">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="O37" s="7">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="P37" s="7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="Q37" s="13"/>
+      <c r="R37" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="S37" s="13"/>
+      <c r="T37" s="7">
+        <v>123</v>
+      </c>
+      <c r="U37" s="7">
+        <v>115</v>
+      </c>
+      <c r="V37" s="7">
+        <v>197</v>
+      </c>
+      <c r="W37" s="13"/>
+      <c r="X37" s="7">
+        <v>97</v>
+      </c>
+      <c r="Y37" s="7">
+        <v>73</v>
+      </c>
+      <c r="Z37" s="7">
+        <v>74</v>
+      </c>
+      <c r="AA37" s="13"/>
+      <c r="AB37" s="7">
+        <v>61</v>
+      </c>
+      <c r="AC37" s="7">
+        <v>41</v>
+      </c>
+      <c r="AD37" s="7">
+        <v>12</v>
+      </c>
+      <c r="AE37" s="13"/>
+      <c r="AI37" s="13"/>
+      <c r="AJ37" s="13"/>
+    </row>
+    <row r="38" spans="1:36" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" s="9">
+        <f t="shared" si="24"/>
+        <v>15</v>
+      </c>
+      <c r="C38" s="9">
+        <f t="shared" si="25"/>
+        <v>14</v>
+      </c>
+      <c r="D38" s="9">
+        <f t="shared" si="26"/>
+        <v>24</v>
+      </c>
+      <c r="E38" s="13"/>
+      <c r="F38" s="9">
+        <f t="shared" si="27"/>
+        <v>26</v>
+      </c>
+      <c r="G38" s="9">
+        <f t="shared" si="28"/>
+        <v>18</v>
+      </c>
+      <c r="H38" s="9">
+        <f t="shared" si="29"/>
         <v>9</v>
       </c>
-      <c r="V47" s="3">
-        <f>ROUND(V43/8.2258064516129, 0)</f>
-        <v>2</v>
-      </c>
-      <c r="W47" s="3"/>
-      <c r="X47" s="3">
-        <f>ROUND(X43/8.2258064516129, 0)</f>
+      <c r="I38" s="13"/>
+      <c r="J38" s="9">
+        <f t="shared" si="30"/>
+        <v>21</v>
+      </c>
+      <c r="K38" s="9">
+        <f t="shared" si="31"/>
+        <v>5</v>
+      </c>
+      <c r="L38" s="9">
+        <f t="shared" si="32"/>
+        <v>12</v>
+      </c>
+      <c r="M38" s="13"/>
+      <c r="N38" s="9">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="O38" s="9">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="P38" s="9">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="Q38" s="13"/>
+      <c r="R38" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="S38" s="13"/>
+      <c r="T38" s="9">
+        <v>123</v>
+      </c>
+      <c r="U38" s="9">
+        <v>115</v>
+      </c>
+      <c r="V38" s="9">
+        <v>197</v>
+      </c>
+      <c r="W38" s="13"/>
+      <c r="X38" s="9">
+        <v>217</v>
+      </c>
+      <c r="Y38" s="9">
+        <v>151</v>
+      </c>
+      <c r="Z38" s="9">
+        <v>70</v>
+      </c>
+      <c r="AA38" s="13"/>
+      <c r="AB38" s="9">
+        <v>171</v>
+      </c>
+      <c r="AC38" s="9">
+        <v>45</v>
+      </c>
+      <c r="AD38" s="9">
+        <v>102</v>
+      </c>
+      <c r="AE38" s="13"/>
+      <c r="AI38" s="13"/>
+      <c r="AJ38" s="13"/>
+    </row>
+    <row r="39" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="Y47" s="3">
-        <f>ROUND(Y43/8.2258064516129, 0)</f>
+      <c r="B39" s="10">
+        <f t="shared" si="24"/>
+        <v>15</v>
+      </c>
+      <c r="C39" s="10">
+        <f t="shared" si="25"/>
+        <v>14</v>
+      </c>
+      <c r="D39" s="10">
+        <f t="shared" si="26"/>
+        <v>24</v>
+      </c>
+      <c r="E39" s="13"/>
+      <c r="F39" s="10">
+        <f t="shared" si="27"/>
+        <v>24</v>
+      </c>
+      <c r="G39" s="10">
+        <f t="shared" si="28"/>
+        <v>24</v>
+      </c>
+      <c r="H39" s="10">
+        <f t="shared" si="29"/>
+        <v>3</v>
+      </c>
+      <c r="I39" s="13"/>
+      <c r="J39" s="10">
+        <f t="shared" si="30"/>
+        <v>24</v>
+      </c>
+      <c r="K39" s="10">
+        <f t="shared" si="31"/>
+        <v>13</v>
+      </c>
+      <c r="L39" s="10">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="M39" s="13"/>
+      <c r="N39" s="10">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="O39" s="10">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="P39" s="10">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="Q39" s="13"/>
+      <c r="R39" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="S39" s="13"/>
+      <c r="T39" s="10">
+        <v>123</v>
+      </c>
+      <c r="U39" s="10">
+        <v>115</v>
+      </c>
+      <c r="V39" s="10">
+        <v>197</v>
+      </c>
+      <c r="W39" s="13"/>
+      <c r="X39" s="10">
+        <v>196</v>
+      </c>
+      <c r="Y39" s="10">
+        <v>196</v>
+      </c>
+      <c r="Z39" s="10">
+        <v>25</v>
+      </c>
+      <c r="AA39" s="13"/>
+      <c r="AB39" s="10">
+        <v>196</v>
+      </c>
+      <c r="AC39" s="10">
+        <v>111</v>
+      </c>
+      <c r="AD39" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="13"/>
+      <c r="AI39" s="13"/>
+      <c r="AJ39" s="13"/>
+    </row>
+    <row r="40" spans="1:36" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" s="11">
+        <f t="shared" si="24"/>
+        <v>15</v>
+      </c>
+      <c r="C40" s="11">
+        <f t="shared" si="25"/>
+        <v>14</v>
+      </c>
+      <c r="D40" s="11">
+        <f t="shared" si="26"/>
+        <v>24</v>
+      </c>
+      <c r="E40" s="13"/>
+      <c r="F40" s="11">
+        <f t="shared" si="27"/>
+        <v>26</v>
+      </c>
+      <c r="G40" s="11">
+        <f t="shared" si="28"/>
+        <v>18</v>
+      </c>
+      <c r="H40" s="11">
+        <f t="shared" si="29"/>
+        <v>9</v>
+      </c>
+      <c r="I40" s="13"/>
+      <c r="J40" s="11">
+        <f t="shared" si="30"/>
+        <v>9</v>
+      </c>
+      <c r="K40" s="11">
+        <f t="shared" si="31"/>
+        <v>11</v>
+      </c>
+      <c r="L40" s="11">
+        <f t="shared" si="32"/>
+        <v>12</v>
+      </c>
+      <c r="M40" s="13"/>
+      <c r="N40" s="11">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="O40" s="11">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="P40" s="11">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="Q40" s="13"/>
+      <c r="R40" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="S40" s="13"/>
+      <c r="T40" s="11">
+        <v>123</v>
+      </c>
+      <c r="U40" s="11">
+        <v>115</v>
+      </c>
+      <c r="V40" s="11">
+        <v>197</v>
+      </c>
+      <c r="W40" s="13"/>
+      <c r="X40" s="11">
+        <v>217</v>
+      </c>
+      <c r="Y40" s="11">
+        <v>151</v>
+      </c>
+      <c r="Z40" s="11">
+        <v>70</v>
+      </c>
+      <c r="AA40" s="13"/>
+      <c r="AB40" s="11">
+        <v>71</v>
+      </c>
+      <c r="AC40" s="11">
+        <v>91</v>
+      </c>
+      <c r="AD40" s="11">
+        <v>97</v>
+      </c>
+      <c r="AE40" s="13"/>
+      <c r="AI40" s="13"/>
+      <c r="AJ40" s="13"/>
+    </row>
+    <row r="41" spans="1:36" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" s="15">
+        <f t="shared" si="24"/>
+        <v>15</v>
+      </c>
+      <c r="C41" s="15">
+        <f t="shared" si="25"/>
+        <v>14</v>
+      </c>
+      <c r="D41" s="15">
+        <f t="shared" si="26"/>
+        <v>24</v>
+      </c>
+      <c r="E41" s="13"/>
+      <c r="F41" s="15">
+        <f t="shared" si="27"/>
+        <v>17</v>
+      </c>
+      <c r="G41" s="15">
+        <f t="shared" si="28"/>
+        <v>17</v>
+      </c>
+      <c r="H41" s="15">
+        <f t="shared" si="29"/>
+        <v>17</v>
+      </c>
+      <c r="I41" s="13"/>
+      <c r="J41" s="15">
+        <f t="shared" si="30"/>
+        <v>6</v>
+      </c>
+      <c r="K41" s="15">
+        <f t="shared" si="31"/>
+        <v>6</v>
+      </c>
+      <c r="L41" s="15">
+        <f t="shared" si="32"/>
+        <v>6</v>
+      </c>
+      <c r="M41" s="13"/>
+      <c r="N41" s="15">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="O41" s="15">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="P41" s="15">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="Q41" s="13"/>
+      <c r="R41" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="S41" s="13"/>
+      <c r="T41" s="15">
+        <v>123</v>
+      </c>
+      <c r="U41" s="15">
+        <v>115</v>
+      </c>
+      <c r="V41" s="15">
+        <v>197</v>
+      </c>
+      <c r="W41" s="13"/>
+      <c r="X41" s="15">
+        <v>140</v>
+      </c>
+      <c r="Y41" s="15">
+        <v>140</v>
+      </c>
+      <c r="Z41" s="15">
+        <v>140</v>
+      </c>
+      <c r="AA41" s="13"/>
+      <c r="AB41" s="15">
+        <v>49</v>
+      </c>
+      <c r="AC41" s="15">
+        <v>49</v>
+      </c>
+      <c r="AD41" s="15">
+        <v>49</v>
+      </c>
+      <c r="AE41" s="13"/>
+      <c r="AI41" s="13"/>
+      <c r="AJ41" s="13"/>
+    </row>
+    <row r="43" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A43" s="13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="13"/>
+      <c r="B44" s="4">
+        <f t="shared" ref="B44:B55" si="36">ROUND(T44/8.2258064516129, 0)</f>
+        <v>29</v>
+      </c>
+      <c r="C44" s="4">
+        <f t="shared" ref="C44:C55" si="37">ROUND(U44/8.2258064516129, 0)</f>
+        <v>21</v>
+      </c>
+      <c r="D44" s="4">
+        <f t="shared" ref="D44:D55" si="38">ROUND(V44/8.2258064516129, 0)</f>
+        <v>14</v>
+      </c>
+      <c r="E44" s="13"/>
+      <c r="I44" s="13"/>
+      <c r="M44" s="13"/>
+      <c r="Q44" s="13"/>
+      <c r="R44" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="S44" s="13"/>
+      <c r="T44" s="4">
+        <v>239</v>
+      </c>
+      <c r="U44" s="4">
+        <v>173</v>
+      </c>
+      <c r="V44" s="4">
+        <v>115</v>
+      </c>
+      <c r="W44" s="13"/>
+      <c r="AA44" s="13"/>
+      <c r="AE44" s="13"/>
+      <c r="AI44" s="13"/>
+      <c r="AJ44" s="13"/>
+    </row>
+    <row r="45" spans="1:36" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="13"/>
+      <c r="B45" s="14">
+        <f t="shared" si="36"/>
+        <v>29</v>
+      </c>
+      <c r="C45" s="14">
+        <f t="shared" si="37"/>
+        <v>21</v>
+      </c>
+      <c r="D45" s="14">
+        <f t="shared" si="38"/>
+        <v>14</v>
+      </c>
+      <c r="E45" s="13"/>
+      <c r="I45" s="13"/>
+      <c r="M45" s="13"/>
+      <c r="Q45" s="13"/>
+      <c r="R45" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="S45" s="13"/>
+      <c r="T45" s="14">
+        <v>239</v>
+      </c>
+      <c r="U45" s="14">
+        <v>173</v>
+      </c>
+      <c r="V45" s="14">
+        <v>115</v>
+      </c>
+      <c r="W45" s="13"/>
+      <c r="AA45" s="13"/>
+      <c r="AE45" s="13"/>
+      <c r="AI45" s="13"/>
+      <c r="AJ45" s="13"/>
+    </row>
+    <row r="46" spans="1:36" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="13"/>
+      <c r="B46" s="5">
+        <f t="shared" si="36"/>
+        <v>29</v>
+      </c>
+      <c r="C46" s="5">
+        <f t="shared" si="37"/>
+        <v>21</v>
+      </c>
+      <c r="D46" s="5">
+        <f t="shared" si="38"/>
+        <v>14</v>
+      </c>
+      <c r="E46" s="13"/>
+      <c r="I46" s="13"/>
+      <c r="M46" s="13"/>
+      <c r="Q46" s="13"/>
+      <c r="R46" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="S46" s="13"/>
+      <c r="T46" s="5">
+        <v>239</v>
+      </c>
+      <c r="U46" s="5">
+        <v>173</v>
+      </c>
+      <c r="V46" s="5">
+        <v>115</v>
+      </c>
+      <c r="W46" s="13"/>
+      <c r="AA46" s="13"/>
+      <c r="AE46" s="13"/>
+      <c r="AI46" s="13"/>
+      <c r="AJ46" s="13"/>
+    </row>
+    <row r="47" spans="1:36" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="13"/>
+      <c r="B47" s="7">
+        <f t="shared" si="36"/>
+        <v>29</v>
+      </c>
+      <c r="C47" s="7">
+        <f t="shared" si="37"/>
+        <v>21</v>
+      </c>
+      <c r="D47" s="7">
+        <f t="shared" si="38"/>
+        <v>14</v>
+      </c>
+      <c r="E47" s="13"/>
+      <c r="I47" s="13"/>
+      <c r="M47" s="13"/>
+      <c r="Q47" s="13"/>
+      <c r="R47" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="S47" s="13"/>
+      <c r="T47" s="7">
+        <v>239</v>
+      </c>
+      <c r="U47" s="7">
+        <v>173</v>
+      </c>
+      <c r="V47" s="7">
+        <v>115</v>
+      </c>
+      <c r="W47" s="13"/>
+      <c r="AA47" s="13"/>
+      <c r="AE47" s="13"/>
+      <c r="AI47" s="13"/>
+      <c r="AJ47" s="13"/>
+    </row>
+    <row r="48" spans="1:36" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="13"/>
+      <c r="B48" s="16">
+        <f t="shared" si="36"/>
+        <v>29</v>
+      </c>
+      <c r="C48" s="16">
+        <f t="shared" si="37"/>
+        <v>21</v>
+      </c>
+      <c r="D48" s="16">
+        <f t="shared" si="38"/>
+        <v>14</v>
+      </c>
+      <c r="E48" s="13"/>
+      <c r="I48" s="13"/>
+      <c r="M48" s="13"/>
+      <c r="Q48" s="13"/>
+      <c r="R48" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="S48" s="13"/>
+      <c r="T48" s="16">
+        <v>239</v>
+      </c>
+      <c r="U48" s="16">
+        <v>173</v>
+      </c>
+      <c r="V48" s="16">
+        <v>115</v>
+      </c>
+      <c r="W48" s="13"/>
+      <c r="AA48" s="13"/>
+      <c r="AE48" s="13"/>
+      <c r="AI48" s="13"/>
+      <c r="AJ48" s="13"/>
+    </row>
+    <row r="49" spans="1:36" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="13"/>
+      <c r="B49" s="6">
+        <f t="shared" si="36"/>
+        <v>29</v>
+      </c>
+      <c r="C49" s="6">
+        <f t="shared" si="37"/>
+        <v>21</v>
+      </c>
+      <c r="D49" s="6">
+        <f t="shared" si="38"/>
+        <v>14</v>
+      </c>
+      <c r="E49" s="13"/>
+      <c r="I49" s="13"/>
+      <c r="M49" s="13"/>
+      <c r="Q49" s="13"/>
+      <c r="R49" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="Z47" s="3">
-        <f>ROUND(Z43/8.2258064516129, 0)</f>
-        <v>9</v>
-      </c>
-      <c r="AA47" s="3"/>
-      <c r="AB47" s="3">
-        <f>ROUND(AB43/8.2258064516129, 0)</f>
-        <v>4</v>
-      </c>
-      <c r="AC47" s="3">
-        <f>ROUND(AC43/8.2258064516129, 0)</f>
-        <v>22</v>
-      </c>
-      <c r="AD47" s="3">
-        <f>ROUND(AD43/8.2258064516129, 0)</f>
-        <v>9</v>
-      </c>
-      <c r="AE47" s="3"/>
-      <c r="AF47" s="3">
-        <f>ROUND(AF43/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="AG47" s="3">
-        <f>ROUND(AG43/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="AH47" s="3">
-        <f>ROUND(AH43/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="48" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="T48" s="3">
-        <f>ROUND(T44/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="U48" s="3">
-        <f>ROUND(U44/8.2258064516129, 0)</f>
-        <v>9</v>
-      </c>
-      <c r="V48" s="3">
-        <f>ROUND(V44/8.2258064516129, 0)</f>
-        <v>2</v>
-      </c>
-      <c r="W48" s="3"/>
-      <c r="X48" s="3">
-        <f>ROUND(X44/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="Y48" s="3">
-        <f>ROUND(Y44/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="Z48" s="3">
-        <f>ROUND(Z44/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="AA48" s="3"/>
-      <c r="AB48" s="3">
-        <f>ROUND(AB44/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="AC48" s="3">
-        <f>ROUND(AC44/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="AD48" s="3">
-        <f>ROUND(AD44/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="AE48" s="3"/>
-      <c r="AF48" s="3">
-        <f>ROUND(AF44/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="AG48" s="3">
-        <f>ROUND(AG44/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
-      <c r="AH48" s="3">
-        <f>ROUND(AH44/8.2258064516129, 0)</f>
-        <v>31</v>
-      </c>
+      <c r="S49" s="13"/>
+      <c r="T49" s="6">
+        <v>239</v>
+      </c>
+      <c r="U49" s="6">
+        <v>173</v>
+      </c>
+      <c r="V49" s="6">
+        <v>115</v>
+      </c>
+      <c r="W49" s="13"/>
+      <c r="AA49" s="13"/>
+      <c r="AE49" s="13"/>
+      <c r="AI49" s="13"/>
+      <c r="AJ49" s="13"/>
+    </row>
+    <row r="50" spans="1:36" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="13"/>
+      <c r="B50" s="8">
+        <f t="shared" si="36"/>
+        <v>29</v>
+      </c>
+      <c r="C50" s="8">
+        <f t="shared" si="37"/>
+        <v>21</v>
+      </c>
+      <c r="D50" s="8">
+        <f t="shared" si="38"/>
+        <v>14</v>
+      </c>
+      <c r="E50" s="13"/>
+      <c r="I50" s="13"/>
+      <c r="M50" s="13"/>
+      <c r="N50" s="8">
+        <f t="shared" ref="N50:P51" si="39">ROUND(AF50/8.2258064516129, 0)</f>
+        <v>6</v>
+      </c>
+      <c r="O50" s="8">
+        <f t="shared" si="39"/>
+        <v>5</v>
+      </c>
+      <c r="P50" s="8">
+        <f t="shared" si="39"/>
+        <v>5</v>
+      </c>
+      <c r="Q50" s="13"/>
+      <c r="R50" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="S50" s="13"/>
+      <c r="T50" s="8">
+        <v>239</v>
+      </c>
+      <c r="U50" s="8">
+        <v>173</v>
+      </c>
+      <c r="V50" s="8">
+        <v>115</v>
+      </c>
+      <c r="W50" s="13"/>
+      <c r="AA50" s="13"/>
+      <c r="AE50" s="13"/>
+      <c r="AF50" s="8">
+        <v>48</v>
+      </c>
+      <c r="AG50" s="8">
+        <v>41</v>
+      </c>
+      <c r="AH50" s="8">
+        <v>41</v>
+      </c>
+      <c r="AI50" s="13"/>
+      <c r="AJ50" s="13"/>
+    </row>
+    <row r="51" spans="1:36" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="13"/>
+      <c r="B51" s="7">
+        <f t="shared" si="36"/>
+        <v>29</v>
+      </c>
+      <c r="C51" s="7">
+        <f t="shared" si="37"/>
+        <v>21</v>
+      </c>
+      <c r="D51" s="7">
+        <f t="shared" si="38"/>
+        <v>14</v>
+      </c>
+      <c r="E51" s="13"/>
+      <c r="I51" s="13"/>
+      <c r="M51" s="13"/>
+      <c r="N51" s="7">
+        <f t="shared" si="39"/>
+        <v>6</v>
+      </c>
+      <c r="O51" s="7">
+        <f t="shared" si="39"/>
+        <v>5</v>
+      </c>
+      <c r="P51" s="7">
+        <f t="shared" si="39"/>
+        <v>5</v>
+      </c>
+      <c r="Q51" s="13"/>
+      <c r="R51" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="S51" s="13"/>
+      <c r="T51" s="7">
+        <v>239</v>
+      </c>
+      <c r="U51" s="7">
+        <v>173</v>
+      </c>
+      <c r="V51" s="7">
+        <v>115</v>
+      </c>
+      <c r="W51" s="13"/>
+      <c r="AA51" s="13"/>
+      <c r="AE51" s="13"/>
+      <c r="AF51" s="7">
+        <v>48</v>
+      </c>
+      <c r="AG51" s="7">
+        <v>41</v>
+      </c>
+      <c r="AH51" s="7">
+        <v>41</v>
+      </c>
+      <c r="AI51" s="13"/>
+      <c r="AJ51" s="13"/>
+    </row>
+    <row r="52" spans="1:36" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="13"/>
+      <c r="B52" s="9">
+        <f t="shared" si="36"/>
+        <v>29</v>
+      </c>
+      <c r="C52" s="9">
+        <f t="shared" si="37"/>
+        <v>21</v>
+      </c>
+      <c r="D52" s="9">
+        <f t="shared" si="38"/>
+        <v>14</v>
+      </c>
+      <c r="E52" s="13"/>
+      <c r="I52" s="13"/>
+      <c r="M52" s="13"/>
+      <c r="Q52" s="13"/>
+      <c r="R52" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="S52" s="13"/>
+      <c r="T52" s="9">
+        <v>239</v>
+      </c>
+      <c r="U52" s="9">
+        <v>173</v>
+      </c>
+      <c r="V52" s="9">
+        <v>115</v>
+      </c>
+      <c r="W52" s="13"/>
+      <c r="AA52" s="13"/>
+      <c r="AE52" s="13"/>
+      <c r="AI52" s="13"/>
+      <c r="AJ52" s="13"/>
+    </row>
+    <row r="53" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="13"/>
+      <c r="B53" s="10">
+        <f t="shared" si="36"/>
+        <v>29</v>
+      </c>
+      <c r="C53" s="10">
+        <f t="shared" si="37"/>
+        <v>21</v>
+      </c>
+      <c r="D53" s="10">
+        <f t="shared" si="38"/>
+        <v>14</v>
+      </c>
+      <c r="E53" s="13"/>
+      <c r="I53" s="13"/>
+      <c r="M53" s="13"/>
+      <c r="Q53" s="13"/>
+      <c r="R53" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="S53" s="13"/>
+      <c r="T53" s="10">
+        <v>239</v>
+      </c>
+      <c r="U53" s="10">
+        <v>173</v>
+      </c>
+      <c r="V53" s="10">
+        <v>115</v>
+      </c>
+      <c r="W53" s="13"/>
+      <c r="AA53" s="13"/>
+      <c r="AE53" s="13"/>
+      <c r="AI53" s="13"/>
+      <c r="AJ53" s="13"/>
+    </row>
+    <row r="54" spans="1:36" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="13"/>
+      <c r="B54" s="11">
+        <f t="shared" si="36"/>
+        <v>29</v>
+      </c>
+      <c r="C54" s="11">
+        <f t="shared" si="37"/>
+        <v>21</v>
+      </c>
+      <c r="D54" s="11">
+        <f t="shared" si="38"/>
+        <v>14</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="M54" s="13"/>
+      <c r="Q54" s="13"/>
+      <c r="R54" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="S54" s="13"/>
+      <c r="T54" s="11">
+        <v>239</v>
+      </c>
+      <c r="U54" s="11">
+        <v>173</v>
+      </c>
+      <c r="V54" s="11">
+        <v>115</v>
+      </c>
+      <c r="W54" s="13"/>
+      <c r="AA54" s="13"/>
+      <c r="AE54" s="13"/>
+      <c r="AI54" s="13"/>
+      <c r="AJ54" s="13"/>
+    </row>
+    <row r="55" spans="1:36" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="13"/>
+      <c r="B55" s="15">
+        <f t="shared" si="36"/>
+        <v>29</v>
+      </c>
+      <c r="C55" s="15">
+        <f t="shared" si="37"/>
+        <v>21</v>
+      </c>
+      <c r="D55" s="15">
+        <f t="shared" si="38"/>
+        <v>14</v>
+      </c>
+      <c r="E55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="M55" s="13"/>
+      <c r="Q55" s="13"/>
+      <c r="R55" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="S55" s="13"/>
+      <c r="T55" s="15">
+        <v>239</v>
+      </c>
+      <c r="U55" s="15">
+        <v>173</v>
+      </c>
+      <c r="V55" s="15">
+        <v>115</v>
+      </c>
+      <c r="W55" s="13"/>
+      <c r="AA55" s="13"/>
+      <c r="AE55" s="13"/>
+      <c r="AI55" s="13"/>
+      <c r="AJ55" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
